--- a/baseline_models/pernio_runs.xlsx
+++ b/baseline_models/pernio_runs.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-6030" windowWidth="16440" windowHeight="28320" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3900" yWindow="345" windowWidth="12150" windowHeight="15585" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="runs" sheetId="1" state="visible" r:id="rId1"/>
@@ -28690,7 +28690,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-05-27 16:34:49</t>
+          <t>2026-05-28 12:43:30</t>
         </is>
       </c>
       <c r="D2" t="b">
@@ -28716,7 +28716,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-05-27 16:35:00</t>
+          <t>2026-05-28 12:43:48</t>
         </is>
       </c>
       <c r="D3" t="b">
@@ -28742,7 +28742,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-05-27 16:35:12</t>
+          <t>2026-05-28 12:44:04</t>
         </is>
       </c>
       <c r="D4" t="b">
@@ -28768,7 +28768,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-05-27 16:35:24</t>
+          <t>2026-05-28 12:44:19</t>
         </is>
       </c>
       <c r="D5" t="b">
@@ -28794,7 +28794,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-05-27 16:35:35</t>
+          <t>2026-05-28 12:44:36</t>
         </is>
       </c>
       <c r="D6" t="b">
@@ -28820,7 +28820,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-05-27 16:35:47</t>
+          <t>2026-05-28 12:44:51</t>
         </is>
       </c>
       <c r="D7" t="b">
@@ -28846,7 +28846,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-05-27 16:35:58</t>
+          <t>2026-05-28 12:45:04</t>
         </is>
       </c>
       <c r="D8" t="b">
@@ -28872,7 +28872,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-05-27 16:36:08</t>
+          <t>2026-05-28 12:45:18</t>
         </is>
       </c>
       <c r="D9" t="b">
@@ -28898,7 +28898,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-05-27 16:36:20</t>
+          <t>2026-05-28 12:45:34</t>
         </is>
       </c>
       <c r="D10" t="b">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-05-27 16:36:31</t>
+          <t>2026-05-28 12:45:49</t>
         </is>
       </c>
       <c r="D11" t="b">
@@ -28950,7 +28950,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-05-27 16:36:42</t>
+          <t>2026-05-28 12:46:03</t>
         </is>
       </c>
       <c r="D12" t="b">
@@ -28976,7 +28976,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-05-27 16:36:53</t>
+          <t>2026-05-28 12:46:17</t>
         </is>
       </c>
       <c r="D13" t="b">
@@ -29002,7 +29002,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-05-27 16:37:04</t>
+          <t>2026-05-28 12:46:30</t>
         </is>
       </c>
       <c r="D14" t="b">
@@ -29028,7 +29028,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-05-27 16:37:16</t>
+          <t>2026-05-28 12:46:45</t>
         </is>
       </c>
       <c r="D15" t="b">
@@ -29054,7 +29054,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-05-27 16:37:27</t>
+          <t>2026-05-28 12:46:59</t>
         </is>
       </c>
       <c r="D16" t="b">
@@ -29080,7 +29080,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-05-27 16:37:38</t>
+          <t>2026-05-28 12:47:13</t>
         </is>
       </c>
       <c r="D17" t="b">
@@ -29106,7 +29106,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-05-27 16:37:49</t>
+          <t>2026-05-28 12:47:28</t>
         </is>
       </c>
       <c r="D18" t="b">
@@ -29132,7 +29132,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-05-27 16:38:01</t>
+          <t>2026-05-28 12:47:47</t>
         </is>
       </c>
       <c r="D19" t="b">
@@ -29158,7 +29158,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-05-27 16:38:12</t>
+          <t>2026-05-28 12:48:04</t>
         </is>
       </c>
       <c r="D20" t="b">
@@ -29184,7 +29184,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-05-27 16:38:23</t>
+          <t>2026-05-28 12:48:22</t>
         </is>
       </c>
       <c r="D21" t="b">
@@ -29210,7 +29210,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-05-27 16:38:34</t>
+          <t>2026-05-28 12:48:45</t>
         </is>
       </c>
       <c r="D22" t="b">
@@ -29236,7 +29236,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-05-27 16:38:46</t>
+          <t>2026-05-28 12:48:59</t>
         </is>
       </c>
       <c r="D23" t="b">
@@ -29262,7 +29262,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-05-27 16:38:57</t>
+          <t>2026-05-28 12:49:12</t>
         </is>
       </c>
       <c r="D24" t="b">
@@ -29288,7 +29288,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-05-27 16:39:09</t>
+          <t>2026-05-28 12:49:25</t>
         </is>
       </c>
       <c r="D25" t="b">
@@ -29314,7 +29314,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-05-27 16:39:20</t>
+          <t>2026-05-28 12:49:40</t>
         </is>
       </c>
       <c r="D26" t="b">
@@ -29340,7 +29340,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-05-27 16:39:32</t>
+          <t>2026-05-28 12:49:58</t>
         </is>
       </c>
       <c r="D27" t="b">
@@ -29366,7 +29366,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-05-27 16:39:43</t>
+          <t>2026-05-28 12:50:16</t>
         </is>
       </c>
       <c r="D28" t="b">
@@ -29392,7 +29392,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-05-27 16:39:54</t>
+          <t>2026-05-28 12:50:30</t>
         </is>
       </c>
       <c r="D29" t="b">
@@ -29418,7 +29418,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-05-27 16:40:12</t>
+          <t>2026-05-28 12:50:52</t>
         </is>
       </c>
       <c r="D30" t="b">
@@ -29444,7 +29444,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-05-27 16:40:34</t>
+          <t>2026-05-28 12:51:16</t>
         </is>
       </c>
       <c r="D31" t="b">
@@ -29470,7 +29470,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-05-27 16:40:47</t>
+          <t>2026-05-28 12:51:31</t>
         </is>
       </c>
       <c r="D32" t="b">
@@ -29496,7 +29496,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-05-27 16:41:00</t>
+          <t>2026-05-28 12:51:45</t>
         </is>
       </c>
       <c r="D33" t="b">
@@ -29522,7 +29522,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-05-27 16:41:12</t>
+          <t>2026-05-28 12:52:02</t>
         </is>
       </c>
       <c r="D34" t="b">
@@ -29548,7 +29548,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-05-27 16:41:24</t>
+          <t>2026-05-28 12:52:19</t>
         </is>
       </c>
       <c r="D35" t="b">
@@ -29574,7 +29574,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-05-27 16:41:37</t>
+          <t>2026-05-28 12:52:37</t>
         </is>
       </c>
       <c r="D36" t="b">
@@ -29600,7 +29600,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-05-27 16:41:49</t>
+          <t>2026-05-28 12:52:55</t>
         </is>
       </c>
       <c r="D37" t="b">
@@ -29626,7 +29626,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-05-27 16:42:04</t>
+          <t>2026-05-28 12:53:10</t>
         </is>
       </c>
       <c r="D38" t="b">
@@ -29652,7 +29652,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-05-27 16:42:17</t>
+          <t>2026-05-28 12:53:25</t>
         </is>
       </c>
       <c r="D39" t="b">
@@ -29678,7 +29678,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-05-27 16:42:29</t>
+          <t>2026-05-28 12:53:41</t>
         </is>
       </c>
       <c r="D40" t="b">
@@ -29704,7 +29704,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-05-27 16:42:42</t>
+          <t>2026-05-28 12:53:57</t>
         </is>
       </c>
       <c r="D41" t="b">
@@ -29730,7 +29730,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-05-27 16:42:54</t>
+          <t>2026-05-28 12:54:12</t>
         </is>
       </c>
       <c r="D42" t="b">
@@ -29756,7 +29756,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-05-27 16:43:07</t>
+          <t>2026-05-28 12:54:32</t>
         </is>
       </c>
       <c r="D43" t="b">
@@ -29782,7 +29782,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-05-27 16:43:19</t>
+          <t>2026-05-28 12:54:50</t>
         </is>
       </c>
       <c r="D44" t="b">
@@ -29808,7 +29808,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-05-27 16:43:30</t>
+          <t>2026-05-28 12:55:03</t>
         </is>
       </c>
       <c r="D45" t="b">
@@ -29834,7 +29834,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-05-27 16:43:42</t>
+          <t>2026-05-28 12:55:23</t>
         </is>
       </c>
       <c r="D46" t="b">
@@ -29860,7 +29860,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-05-27 16:43:54</t>
+          <t>2026-05-28 12:55:40</t>
         </is>
       </c>
       <c r="D47" t="b">
@@ -29886,7 +29886,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-05-27 16:44:06</t>
+          <t>2026-05-28 12:55:55</t>
         </is>
       </c>
       <c r="D48" t="b">
@@ -29912,7 +29912,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-05-27 16:44:17</t>
+          <t>2026-05-28 12:56:11</t>
         </is>
       </c>
       <c r="D49" t="b">
@@ -29938,7 +29938,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-05-27 16:44:29</t>
+          <t>2026-05-28 12:56:29</t>
         </is>
       </c>
       <c r="D50" t="b">
@@ -29964,7 +29964,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-05-27 16:44:41</t>
+          <t>2026-05-28 12:56:43</t>
         </is>
       </c>
       <c r="D51" t="b">
@@ -29990,7 +29990,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-05-27 16:44:53</t>
+          <t>2026-05-28 12:56:57</t>
         </is>
       </c>
       <c r="D52" t="b">
@@ -30016,7 +30016,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-05-27 16:45:05</t>
+          <t>2026-05-28 12:57:11</t>
         </is>
       </c>
       <c r="D53" t="b">
@@ -30042,7 +30042,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-05-27 16:45:17</t>
+          <t>2026-05-28 12:57:26</t>
         </is>
       </c>
       <c r="D54" t="b">
@@ -30068,7 +30068,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-05-27 16:45:30</t>
+          <t>2026-05-28 12:57:40</t>
         </is>
       </c>
       <c r="D55" t="b">
@@ -30094,7 +30094,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-05-27 16:45:42</t>
+          <t>2026-05-28 12:57:55</t>
         </is>
       </c>
       <c r="D56" t="b">
@@ -30120,7 +30120,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-05-27 16:45:53</t>
+          <t>2026-05-28 12:58:09</t>
         </is>
       </c>
       <c r="D57" t="b">
@@ -30146,7 +30146,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-05-27 16:46:11</t>
+          <t>2026-05-28 12:58:35</t>
         </is>
       </c>
       <c r="D58" t="b">
@@ -30172,7 +30172,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-05-27 16:46:29</t>
+          <t>2026-05-28 12:58:59</t>
         </is>
       </c>
       <c r="D59" t="b">
@@ -30198,7 +30198,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-05-27 16:46:39</t>
+          <t>2026-05-28 12:59:12</t>
         </is>
       </c>
       <c r="D60" t="b">
@@ -30224,7 +30224,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-05-27 16:46:51</t>
+          <t>2026-05-28 12:59:26</t>
         </is>
       </c>
       <c r="D61" t="b">
@@ -30250,7 +30250,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-05-27 16:47:10</t>
+          <t>2026-05-28 12:59:48</t>
         </is>
       </c>
       <c r="D62" t="b">
@@ -30276,7 +30276,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-05-27 16:47:28</t>
+          <t>2026-05-28 13:00:09</t>
         </is>
       </c>
       <c r="D63" t="b">
@@ -30302,7 +30302,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-05-27 16:47:39</t>
+          <t>2026-05-28 13:00:22</t>
         </is>
       </c>
       <c r="D64" t="b">
@@ -30328,7 +30328,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-05-27 16:47:51</t>
+          <t>2026-05-28 13:00:36</t>
         </is>
       </c>
       <c r="D65" t="b">
@@ -30354,7 +30354,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-05-27 16:48:09</t>
+          <t>2026-05-28 13:01:05</t>
         </is>
       </c>
       <c r="D66" t="b">
@@ -30380,7 +30380,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-05-27 16:48:27</t>
+          <t>2026-05-28 13:01:35</t>
         </is>
       </c>
       <c r="D67" t="b">

--- a/baseline_models/pernio_runs.xlsx
+++ b/baseline_models/pernio_runs.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-28920" yWindow="-315" windowWidth="29040" windowHeight="17520" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="runs" sheetId="1" state="visible" r:id="rId1"/>
@@ -50,7 +50,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -109,6 +109,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -132,7 +144,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -187,17 +199,8 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -567,13 +570,13 @@
   <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" style="35" min="1" max="1"/>
-    <col width="22.7109375" customWidth="1" style="35" min="2" max="2"/>
-    <col width="14" customWidth="1" style="35" min="3" max="3"/>
-    <col width="23" customWidth="1" style="35" min="4" max="4"/>
-    <col width="9" customWidth="1" style="35" min="5" max="5"/>
-    <col width="15" customWidth="1" style="35" min="6" max="6"/>
-    <col width="10" customWidth="1" style="35" min="7" max="7"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="22.7109375" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1285,769 +1288,769 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="23" customFormat="1" s="32">
+      <c r="A23" s="32" t="inlineStr">
         <is>
           <t>10.0.0</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="32" t="inlineStr">
         <is>
           <t>RY5 gen avg</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="32" t="inlineStr">
         <is>
           <t>Original</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="32" t="inlineStr">
         <is>
           <t>Original</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" s="32" t="inlineStr">
         <is>
           <t>BOTH</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" s="32" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="24" customFormat="1" s="32">
+      <c r="A24" s="32" t="inlineStr">
         <is>
           <t>10.10.0</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="32" t="inlineStr">
         <is>
           <t>RY5 gen avg</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="32" t="inlineStr">
         <is>
           <t>RY5 gen avg</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="32" t="inlineStr">
         <is>
           <t>Original</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="32" t="inlineStr">
         <is>
           <t>BOTH</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" s="32" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="25" customFormat="1" s="32">
+      <c r="A25" s="32" t="inlineStr">
         <is>
           <t>10.0.1</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="32" t="inlineStr">
         <is>
           <t>RY5 gen avg</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="32" t="inlineStr">
         <is>
           <t>Original</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="32" t="inlineStr">
         <is>
           <t>Sand associative</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" s="32" t="inlineStr">
         <is>
           <t>BOTH</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G25" s="32" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="26" customFormat="1" s="32">
+      <c r="A26" s="32" t="inlineStr">
         <is>
           <t>10.10.1</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="32" t="inlineStr">
         <is>
           <t>RY5 gen avg</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="32" t="inlineStr">
         <is>
           <t>RY5 gen avg</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="32" t="inlineStr">
         <is>
           <t>Sand associative</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" s="32" t="inlineStr">
         <is>
           <t>BOTH</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" s="32" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="27" customFormat="1" s="32">
+      <c r="A27" s="32" t="inlineStr">
         <is>
           <t>10.0.2</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="32" t="inlineStr">
         <is>
           <t>RY5 gen avg</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="32" t="inlineStr">
         <is>
           <t>Original</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="32" t="inlineStr">
         <is>
           <t>Sand non-associative</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" s="32" t="inlineStr">
         <is>
           <t>BOTH</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" s="32" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="28" customFormat="1" s="32">
+      <c r="A28" s="32" t="inlineStr">
         <is>
           <t>10.10.2</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="32" t="inlineStr">
         <is>
           <t>RY5 gen avg</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="32" t="inlineStr">
         <is>
           <t>RY5 gen avg</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="32" t="inlineStr">
         <is>
           <t>Sand non-associative</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" s="32" t="inlineStr">
         <is>
           <t>BOTH</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G28" s="32" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="29" customFormat="1" s="33">
+      <c r="A29" s="33" t="inlineStr">
         <is>
           <t>11.0.0</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="33" t="inlineStr">
         <is>
           <t>RY5 gen caut</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="33" t="inlineStr">
         <is>
           <t>Original</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="33" t="inlineStr">
         <is>
           <t>Original</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" s="33" t="inlineStr">
         <is>
           <t>BOTH</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G29" s="33" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="30" customFormat="1" s="33">
+      <c r="A30" s="33" t="inlineStr">
         <is>
           <t>11.11.0</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="33" t="inlineStr">
         <is>
           <t>RY5 gen caut</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="33" t="inlineStr">
         <is>
           <t>RY5 gen caut</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="33" t="inlineStr">
         <is>
           <t>Original</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" s="33" t="inlineStr">
         <is>
           <t>BOTH</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G30" s="33" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="31" customFormat="1" s="33">
+      <c r="A31" s="33" t="inlineStr">
         <is>
           <t>11.0.1</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="33" t="inlineStr">
         <is>
           <t>RY5 gen caut</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="33" t="inlineStr">
         <is>
           <t>Original</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="33" t="inlineStr">
         <is>
           <t>Sand associative</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F31" s="33" t="inlineStr">
         <is>
           <t>BOTH</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G31" s="33" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="32" customFormat="1" s="33">
+      <c r="A32" s="33" t="inlineStr">
         <is>
           <t>11.11.1</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="33" t="inlineStr">
         <is>
           <t>RY5 gen caut</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="33" t="inlineStr">
         <is>
           <t>RY5 gen caut</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="33" t="inlineStr">
         <is>
           <t>Sand associative</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" s="33" t="inlineStr">
         <is>
           <t>BOTH</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G32" s="33" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+    <row r="33" customFormat="1" s="33">
+      <c r="A33" s="33" t="inlineStr">
         <is>
           <t>11.0.2</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="33" t="inlineStr">
         <is>
           <t>RY5 gen caut</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="33" t="inlineStr">
         <is>
           <t>Original</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="33" t="inlineStr">
         <is>
           <t>Sand non-associative</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" s="33" t="inlineStr">
         <is>
           <t>BOTH</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G33" s="33" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+    <row r="34" ht="15.75" customFormat="1" customHeight="1" s="33">
+      <c r="A34" s="33" t="inlineStr">
         <is>
           <t>11.11.2</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="33" t="inlineStr">
         <is>
           <t>RY5 gen caut</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="33" t="inlineStr">
         <is>
           <t>RY5 gen caut</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="33" t="inlineStr">
         <is>
           <t>Sand non-associative</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" s="33" t="inlineStr">
         <is>
           <t>BOTH</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G34" s="33" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+    <row r="35" customFormat="1" s="32">
+      <c r="A35" s="32" t="inlineStr">
         <is>
           <t>13.0.0</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="32" t="inlineStr">
         <is>
           <t>RY5 gen avg+(clay int)</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="32" t="inlineStr">
         <is>
           <t>Original</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="32" t="inlineStr">
         <is>
           <t>Original</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" s="32" t="inlineStr">
         <is>
           <t>BOTH</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G35" s="32" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+    <row r="36" customFormat="1" s="32">
+      <c r="A36" s="32" t="inlineStr">
         <is>
           <t>13.13.0</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="32" t="inlineStr">
         <is>
           <t>RY5 gen avg+(clay int)</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="32" t="inlineStr">
         <is>
           <t>RY5 gen avg</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" s="32" t="inlineStr">
         <is>
           <t>Original</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" s="32" t="inlineStr">
         <is>
           <t>BOTH</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G36" s="32" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+    <row r="37" customFormat="1" s="32">
+      <c r="A37" s="32" t="inlineStr">
         <is>
           <t>13.0.1</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="32" t="inlineStr">
         <is>
           <t>RY5 gen avg+(clay int)</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="32" t="inlineStr">
         <is>
           <t>Original</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" s="32" t="inlineStr">
         <is>
           <t>Sand associative+int</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" s="32" t="inlineStr">
         <is>
           <t>BOTH</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G37" s="32" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+    <row r="38" customFormat="1" s="32">
+      <c r="A38" s="32" t="inlineStr">
         <is>
           <t>13.13.1</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="32" t="inlineStr">
         <is>
           <t>RY5 gen avg+(clay int)</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="32" t="inlineStr">
         <is>
           <t>RY5 gen avg</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" s="32" t="inlineStr">
         <is>
           <t>Sand associative+int</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" s="32" t="inlineStr">
         <is>
           <t>BOTH</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G38" s="32" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+    <row r="39" customFormat="1" s="32">
+      <c r="A39" s="32" t="inlineStr">
         <is>
           <t>13.0.2</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="32" t="inlineStr">
         <is>
           <t>RY5 gen avg+(clay int)</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="32" t="inlineStr">
         <is>
           <t>Original</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" s="32" t="inlineStr">
         <is>
           <t>Sand non-associative+int</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" s="32" t="inlineStr">
         <is>
           <t>BOTH</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G39" s="32" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+    <row r="40" customFormat="1" s="32">
+      <c r="A40" s="32" t="inlineStr">
         <is>
           <t>13.13.2</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="32" t="inlineStr">
         <is>
           <t>RY5 gen avg+(clay int)</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="32" t="inlineStr">
         <is>
           <t>RY5 gen avg</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D40" s="32" t="inlineStr">
         <is>
           <t>Sand non-associative+int</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F40" s="32" t="inlineStr">
         <is>
           <t>BOTH</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G40" s="32" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+    <row r="41" customFormat="1" s="33">
+      <c r="A41" s="33" t="inlineStr">
         <is>
           <t>14.0.0</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="33" t="inlineStr">
         <is>
           <t>RY5 gen caut+(clay int)</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="33" t="inlineStr">
         <is>
           <t>Original</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" s="33" t="inlineStr">
         <is>
           <t>Original</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F41" s="33" t="inlineStr">
         <is>
           <t>BOTH</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G41" s="33" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="42" customFormat="1" s="33">
+      <c r="A42" s="33" t="inlineStr">
         <is>
           <t>14.14.0</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="33" t="inlineStr">
         <is>
           <t>RY5 gen caut+(clay int)</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="33" t="inlineStr">
         <is>
           <t>RY5 gen caut</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D42" s="33" t="inlineStr">
         <is>
           <t>Original</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F42" s="33" t="inlineStr">
         <is>
           <t>BOTH</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G42" s="33" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+    <row r="43" customFormat="1" s="33">
+      <c r="A43" s="33" t="inlineStr">
         <is>
           <t>14.0.1</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="33" t="inlineStr">
         <is>
           <t>RY5 gen caut+(clay int)</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="33" t="inlineStr">
         <is>
           <t>Original</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" s="33" t="inlineStr">
         <is>
           <t>Sand associative+int</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F43" s="33" t="inlineStr">
         <is>
           <t>BOTH</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G43" s="33" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+    <row r="44" customFormat="1" s="33">
+      <c r="A44" s="33" t="inlineStr">
         <is>
           <t>14.14.1</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="33" t="inlineStr">
         <is>
           <t>RY5 gen caut+(clay int)</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="33" t="inlineStr">
         <is>
           <t>RY5 gen caut</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" s="33" t="inlineStr">
         <is>
           <t>Sand associative+int</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F44" s="33" t="inlineStr">
         <is>
           <t>BOTH</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G44" s="33" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+    <row r="45" customFormat="1" s="33">
+      <c r="A45" s="33" t="inlineStr">
         <is>
           <t>14.0.2</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="33" t="inlineStr">
         <is>
           <t>RY5 gen caut+(clay int)</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="33" t="inlineStr">
         <is>
           <t>Original</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" s="33" t="inlineStr">
         <is>
           <t>Sand non-associative+int</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F45" s="33" t="inlineStr">
         <is>
           <t>BOTH</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G45" s="33" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+    <row r="46" customFormat="1" s="33">
+      <c r="A46" s="33" t="inlineStr">
         <is>
           <t>14.14.2</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="33" t="inlineStr">
         <is>
           <t>RY5 gen caut+(clay int)</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="33" t="inlineStr">
         <is>
           <t>RY5 gen caut</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" s="33" t="inlineStr">
         <is>
           <t>Sand non-associative+int</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F46" s="33" t="inlineStr">
         <is>
           <t>BOTH</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G46" s="33" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2260,19 +2263,19 @@
   <dimension ref="A1:P817"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9.85546875" customWidth="1" style="35" min="1" max="1"/>
-    <col width="40.28515625" bestFit="1" customWidth="1" style="35" min="2" max="2"/>
-    <col width="23" customWidth="1" style="35" min="3" max="3"/>
-    <col width="27.5703125" customWidth="1" style="35" min="4" max="4"/>
-    <col width="19.85546875" customWidth="1" style="35" min="5" max="5"/>
-    <col width="17.28515625" customWidth="1" style="35" min="6" max="6"/>
-    <col width="13" customWidth="1" style="35" min="7" max="8"/>
-    <col width="8" customWidth="1" style="35" min="9" max="10"/>
-    <col width="10" customWidth="1" style="35" min="11" max="11"/>
-    <col width="8" customWidth="1" style="35" min="12" max="12"/>
-    <col width="10" customWidth="1" style="35" min="13" max="13"/>
-    <col width="16" customWidth="1" style="35" min="14" max="14"/>
-    <col width="14" customWidth="1" style="35" min="15" max="16"/>
+    <col width="9.85546875" customWidth="1" min="1" max="1"/>
+    <col width="40.28515625" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="27.5703125" customWidth="1" min="4" max="4"/>
+    <col width="19.85546875" customWidth="1" min="5" max="5"/>
+    <col width="17.28515625" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="8"/>
+    <col width="8" customWidth="1" min="9" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3294,45 +3297,45 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" customFormat="1" s="36">
-      <c r="A20" s="36" t="inlineStr">
+    <row r="20" customFormat="1" s="3">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>0.0.1</t>
         </is>
       </c>
-      <c r="B20" s="36" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Embankment / associative</t>
         </is>
       </c>
-      <c r="C20" s="36" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>1_embankment</t>
         </is>
       </c>
-      <c r="E20" s="36" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>L 23, L 24</t>
         </is>
       </c>
-      <c r="F20" s="37" t="inlineStr">
+      <c r="F20" s="7" t="inlineStr">
         <is>
           <t>MohrCoulombClassic</t>
         </is>
       </c>
-      <c r="G20" s="36" t="n">
+      <c r="G20" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="H20" s="36" t="n">
+      <c r="H20" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="K20" s="37" t="n">
+      <c r="K20" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="L20" s="37" t="n">
+      <c r="L20" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="P20" s="38" t="n"/>
+      <c r="P20" s="4" t="n"/>
     </row>
     <row r="21" customFormat="1" s="27">
       <c r="A21" s="27" t="inlineStr">
@@ -3379,48 +3382,48 @@
       </c>
       <c r="P21" s="29" t="n"/>
     </row>
-    <row r="22" customFormat="1" s="36">
-      <c r="A22" s="36" t="inlineStr">
+    <row r="22" customFormat="1" s="3">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>0.0.2</t>
         </is>
       </c>
-      <c r="B22" s="36" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Embankment / non-associative</t>
         </is>
       </c>
-      <c r="C22" s="36" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>1_embankment</t>
         </is>
       </c>
-      <c r="E22" s="36" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>L 23, L 24</t>
         </is>
       </c>
-      <c r="F22" s="37" t="inlineStr">
+      <c r="F22" s="7" t="inlineStr">
         <is>
           <t>MohrCoulombAdvanced</t>
         </is>
       </c>
-      <c r="G22" s="36" t="n">
+      <c r="G22" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="H22" s="36" t="n">
+      <c r="H22" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="K22" s="37" t="n">
+      <c r="K22" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="L22" s="37" t="n">
+      <c r="L22" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="M22" s="37" t="n">
+      <c r="M22" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="P22" s="38" t="n"/>
+      <c r="P22" s="4" t="n"/>
     </row>
     <row r="23" customFormat="1" s="27">
       <c r="A23" s="27" t="inlineStr">
@@ -5062,90 +5065,90 @@
         <v>48.51</v>
       </c>
     </row>
-    <row r="54" customFormat="1" s="36">
-      <c r="A54" s="36" t="inlineStr">
+    <row r="54" customFormat="1" s="3">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>3.0.1</t>
         </is>
       </c>
-      <c r="B54" s="36" t="inlineStr">
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t>Embankment / associative</t>
         </is>
       </c>
-      <c r="C54" s="36" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t>1_embankment</t>
         </is>
       </c>
-      <c r="E54" s="36" t="inlineStr">
+      <c r="E54" s="3" t="inlineStr">
         <is>
           <t>L 23, L 24</t>
         </is>
       </c>
-      <c r="F54" s="37" t="inlineStr">
+      <c r="F54" s="7" t="inlineStr">
         <is>
           <t>MohrCoulombClassic</t>
         </is>
       </c>
-      <c r="G54" s="36" t="n">
+      <c r="G54" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="H54" s="36" t="n">
+      <c r="H54" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="K54" s="37" t="n">
+      <c r="K54" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="L54" s="37" t="n">
+      <c r="L54" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="P54" s="38" t="n"/>
-    </row>
-    <row r="55" customFormat="1" s="32">
-      <c r="A55" s="32" t="inlineStr">
+      <c r="P54" s="4" t="n"/>
+    </row>
+    <row r="55" customFormat="1" s="5">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>3.0.1</t>
         </is>
       </c>
-      <c r="B55" s="32" t="inlineStr">
+      <c r="B55" s="5" t="inlineStr">
         <is>
           <t>Sand fill / associative</t>
         </is>
       </c>
-      <c r="C55" s="32" t="inlineStr">
+      <c r="C55" s="5" t="inlineStr">
         <is>
           <t>2_sand_fill</t>
         </is>
       </c>
-      <c r="D55" s="32" t="inlineStr">
+      <c r="D55" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 23, L 22, L 19, L 20</t>
         </is>
       </c>
-      <c r="E55" s="32" t="inlineStr">
+      <c r="E55" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 20, L 25</t>
         </is>
       </c>
-      <c r="F55" s="33" t="inlineStr">
+      <c r="F55" s="30" t="inlineStr">
         <is>
           <t>MohrCoulombClassic</t>
         </is>
       </c>
-      <c r="G55" s="32" t="n">
+      <c r="G55" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="H55" s="32" t="n">
+      <c r="H55" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="K55" s="33" t="n">
+      <c r="K55" s="30" t="n">
         <v>36</v>
       </c>
-      <c r="L55" s="33" t="n">
+      <c r="L55" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="P55" s="34" t="n"/>
+      <c r="P55" s="6" t="n"/>
     </row>
     <row r="56" customFormat="1" s="8">
       <c r="A56" s="8" t="inlineStr">
@@ -5957,90 +5960,90 @@
         </is>
       </c>
     </row>
-    <row r="71" customFormat="1" s="36">
-      <c r="A71" s="36" t="inlineStr">
+    <row r="71" customFormat="1" s="3">
+      <c r="A71" s="3" t="inlineStr">
         <is>
           <t>3.3.1</t>
         </is>
       </c>
-      <c r="B71" s="36" t="inlineStr">
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t>Embankment / associative</t>
         </is>
       </c>
-      <c r="C71" s="36" t="inlineStr">
+      <c r="C71" s="3" t="inlineStr">
         <is>
           <t>1_embankment</t>
         </is>
       </c>
-      <c r="E71" s="36" t="inlineStr">
+      <c r="E71" s="3" t="inlineStr">
         <is>
           <t>L 23, L 24</t>
         </is>
       </c>
-      <c r="F71" s="37" t="inlineStr">
+      <c r="F71" s="7" t="inlineStr">
         <is>
           <t>MohrCoulombClassic</t>
         </is>
       </c>
-      <c r="G71" s="36" t="n">
+      <c r="G71" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="H71" s="36" t="n">
+      <c r="H71" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="K71" s="37" t="n">
+      <c r="K71" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="L71" s="37" t="n">
+      <c r="L71" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="P71" s="38" t="n"/>
-    </row>
-    <row r="72" customFormat="1" s="32">
-      <c r="A72" s="32" t="inlineStr">
+      <c r="P71" s="4" t="n"/>
+    </row>
+    <row r="72" customFormat="1" s="5">
+      <c r="A72" s="5" t="inlineStr">
         <is>
           <t>3.3.1</t>
         </is>
       </c>
-      <c r="B72" s="32" t="inlineStr">
+      <c r="B72" s="5" t="inlineStr">
         <is>
           <t>Sand fill / associative</t>
         </is>
       </c>
-      <c r="C72" s="32" t="inlineStr">
+      <c r="C72" s="5" t="inlineStr">
         <is>
           <t>2_sand_fill</t>
         </is>
       </c>
-      <c r="D72" s="32" t="inlineStr">
+      <c r="D72" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 23, L 22, L 19, L 20</t>
         </is>
       </c>
-      <c r="E72" s="32" t="inlineStr">
+      <c r="E72" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 20, L 25</t>
         </is>
       </c>
-      <c r="F72" s="33" t="inlineStr">
+      <c r="F72" s="30" t="inlineStr">
         <is>
           <t>MohrCoulombClassic</t>
         </is>
       </c>
-      <c r="G72" s="32" t="n">
+      <c r="G72" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="H72" s="32" t="n">
+      <c r="H72" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="K72" s="33" t="n">
+      <c r="K72" s="30" t="n">
         <v>36</v>
       </c>
-      <c r="L72" s="33" t="n">
+      <c r="L72" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="P72" s="34" t="n"/>
+      <c r="P72" s="6" t="n"/>
     </row>
     <row r="73" customFormat="1" s="8">
       <c r="A73" s="8" t="inlineStr">
@@ -6824,96 +6827,96 @@
         <v>48.51</v>
       </c>
     </row>
-    <row r="88" customFormat="1" s="36">
-      <c r="A88" s="36" t="inlineStr">
+    <row r="88" customFormat="1" s="3">
+      <c r="A88" s="3" t="inlineStr">
         <is>
           <t>3.0.2</t>
         </is>
       </c>
-      <c r="B88" s="36" t="inlineStr">
+      <c r="B88" s="3" t="inlineStr">
         <is>
           <t>Embankment / non-associative</t>
         </is>
       </c>
-      <c r="C88" s="36" t="inlineStr">
+      <c r="C88" s="3" t="inlineStr">
         <is>
           <t>1_embankment</t>
         </is>
       </c>
-      <c r="E88" s="36" t="inlineStr">
+      <c r="E88" s="3" t="inlineStr">
         <is>
           <t>L 23, L 24</t>
         </is>
       </c>
-      <c r="F88" s="37" t="inlineStr">
+      <c r="F88" s="7" t="inlineStr">
         <is>
           <t>MohrCoulombAdvanced</t>
         </is>
       </c>
-      <c r="G88" s="36" t="n">
+      <c r="G88" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="H88" s="36" t="n">
+      <c r="H88" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="K88" s="37" t="n">
+      <c r="K88" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="L88" s="37" t="n">
+      <c r="L88" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="M88" s="37" t="n">
+      <c r="M88" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="P88" s="38" t="n"/>
-    </row>
-    <row r="89" customFormat="1" s="32">
-      <c r="A89" s="32" t="inlineStr">
+      <c r="P88" s="4" t="n"/>
+    </row>
+    <row r="89" customFormat="1" s="5">
+      <c r="A89" s="5" t="inlineStr">
         <is>
           <t>3.0.2</t>
         </is>
       </c>
-      <c r="B89" s="32" t="inlineStr">
+      <c r="B89" s="5" t="inlineStr">
         <is>
           <t>Sand fill / non-associative</t>
         </is>
       </c>
-      <c r="C89" s="32" t="inlineStr">
+      <c r="C89" s="5" t="inlineStr">
         <is>
           <t>2_sand_fill</t>
         </is>
       </c>
-      <c r="D89" s="32" t="inlineStr">
+      <c r="D89" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 23, L 22, L 19, L 20</t>
         </is>
       </c>
-      <c r="E89" s="32" t="inlineStr">
+      <c r="E89" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 20, L 25</t>
         </is>
       </c>
-      <c r="F89" s="33" t="inlineStr">
+      <c r="F89" s="30" t="inlineStr">
         <is>
           <t>MohrCoulombAdvanced</t>
         </is>
       </c>
-      <c r="G89" s="32" t="n">
+      <c r="G89" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="H89" s="32" t="n">
+      <c r="H89" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="K89" s="33" t="n">
+      <c r="K89" s="30" t="n">
         <v>36</v>
       </c>
-      <c r="L89" s="33" t="n">
+      <c r="L89" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="M89" s="33" t="n">
+      <c r="M89" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="P89" s="34" t="n"/>
+      <c r="P89" s="6" t="n"/>
     </row>
     <row r="90" customFormat="1" s="8">
       <c r="A90" s="8" t="inlineStr">
@@ -7725,96 +7728,96 @@
         </is>
       </c>
     </row>
-    <row r="105" customFormat="1" s="36">
-      <c r="A105" s="36" t="inlineStr">
+    <row r="105" customFormat="1" s="3">
+      <c r="A105" s="3" t="inlineStr">
         <is>
           <t>3.3.2</t>
         </is>
       </c>
-      <c r="B105" s="36" t="inlineStr">
+      <c r="B105" s="3" t="inlineStr">
         <is>
           <t>Embankment / non-associative</t>
         </is>
       </c>
-      <c r="C105" s="36" t="inlineStr">
+      <c r="C105" s="3" t="inlineStr">
         <is>
           <t>1_embankment</t>
         </is>
       </c>
-      <c r="E105" s="36" t="inlineStr">
+      <c r="E105" s="3" t="inlineStr">
         <is>
           <t>L 23, L 24</t>
         </is>
       </c>
-      <c r="F105" s="37" t="inlineStr">
+      <c r="F105" s="7" t="inlineStr">
         <is>
           <t>MohrCoulombAdvanced</t>
         </is>
       </c>
-      <c r="G105" s="36" t="n">
+      <c r="G105" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="H105" s="36" t="n">
+      <c r="H105" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="K105" s="37" t="n">
+      <c r="K105" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="L105" s="37" t="n">
+      <c r="L105" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="M105" s="37" t="n">
+      <c r="M105" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="P105" s="38" t="n"/>
-    </row>
-    <row r="106" customFormat="1" s="32">
-      <c r="A106" s="32" t="inlineStr">
+      <c r="P105" s="4" t="n"/>
+    </row>
+    <row r="106" customFormat="1" s="5">
+      <c r="A106" s="5" t="inlineStr">
         <is>
           <t>3.3.2</t>
         </is>
       </c>
-      <c r="B106" s="32" t="inlineStr">
+      <c r="B106" s="5" t="inlineStr">
         <is>
           <t>Sand fill / non-associative</t>
         </is>
       </c>
-      <c r="C106" s="32" t="inlineStr">
+      <c r="C106" s="5" t="inlineStr">
         <is>
           <t>2_sand_fill</t>
         </is>
       </c>
-      <c r="D106" s="32" t="inlineStr">
+      <c r="D106" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 23, L 22, L 19, L 20</t>
         </is>
       </c>
-      <c r="E106" s="32" t="inlineStr">
+      <c r="E106" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 20, L 25</t>
         </is>
       </c>
-      <c r="F106" s="33" t="inlineStr">
+      <c r="F106" s="30" t="inlineStr">
         <is>
           <t>MohrCoulombAdvanced</t>
         </is>
       </c>
-      <c r="G106" s="32" t="n">
+      <c r="G106" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="H106" s="32" t="n">
+      <c r="H106" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="K106" s="33" t="n">
+      <c r="K106" s="30" t="n">
         <v>36</v>
       </c>
-      <c r="L106" s="33" t="n">
+      <c r="L106" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="M106" s="33" t="n">
+      <c r="M106" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="P106" s="34" t="n"/>
+      <c r="P106" s="6" t="n"/>
     </row>
     <row r="107" customFormat="1" s="8">
       <c r="A107" s="8" t="inlineStr">
@@ -10200,90 +10203,90 @@
         <v>48.51</v>
       </c>
     </row>
-    <row r="152" customFormat="1" s="36">
-      <c r="A152" s="36" t="inlineStr">
+    <row r="152" customFormat="1" s="3">
+      <c r="A152" s="3" t="inlineStr">
         <is>
           <t>4.0.1</t>
         </is>
       </c>
-      <c r="B152" s="36" t="inlineStr">
+      <c r="B152" s="3" t="inlineStr">
         <is>
           <t>Embankment / associative</t>
         </is>
       </c>
-      <c r="C152" s="36" t="inlineStr">
+      <c r="C152" s="3" t="inlineStr">
         <is>
           <t>1_embankment</t>
         </is>
       </c>
-      <c r="E152" s="36" t="inlineStr">
+      <c r="E152" s="3" t="inlineStr">
         <is>
           <t>L 23, L 24</t>
         </is>
       </c>
-      <c r="F152" s="36" t="inlineStr">
+      <c r="F152" s="3" t="inlineStr">
         <is>
           <t>MohrCoulombClassic</t>
         </is>
       </c>
-      <c r="G152" s="36" t="n">
+      <c r="G152" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="H152" s="36" t="n">
+      <c r="H152" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="K152" s="36" t="n">
+      <c r="K152" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="L152" s="36" t="n">
+      <c r="L152" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="P152" s="38" t="n"/>
-    </row>
-    <row r="153" customFormat="1" s="32">
-      <c r="A153" s="32" t="inlineStr">
+      <c r="P152" s="4" t="n"/>
+    </row>
+    <row r="153" customFormat="1" s="5">
+      <c r="A153" s="5" t="inlineStr">
         <is>
           <t>4.0.1</t>
         </is>
       </c>
-      <c r="B153" s="32" t="inlineStr">
+      <c r="B153" s="5" t="inlineStr">
         <is>
           <t>Sand fill / associative</t>
         </is>
       </c>
-      <c r="C153" s="32" t="inlineStr">
+      <c r="C153" s="5" t="inlineStr">
         <is>
           <t>2_sand_fill</t>
         </is>
       </c>
-      <c r="D153" s="32" t="inlineStr">
+      <c r="D153" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 23, L 22, L 19, L 20</t>
         </is>
       </c>
-      <c r="E153" s="32" t="inlineStr">
+      <c r="E153" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 20, L 25</t>
         </is>
       </c>
-      <c r="F153" s="32" t="inlineStr">
+      <c r="F153" s="5" t="inlineStr">
         <is>
           <t>MohrCoulombClassic</t>
         </is>
       </c>
-      <c r="G153" s="32" t="n">
+      <c r="G153" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="H153" s="32" t="n">
+      <c r="H153" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="K153" s="32" t="n">
+      <c r="K153" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="L153" s="32" t="n">
+      <c r="L153" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="P153" s="34" t="n"/>
+      <c r="P153" s="6" t="n"/>
     </row>
     <row r="154" customFormat="1" s="8">
       <c r="A154" s="8" t="inlineStr">
@@ -11100,90 +11103,90 @@
         </is>
       </c>
     </row>
-    <row r="169" customFormat="1" s="36">
-      <c r="A169" s="36" t="inlineStr">
+    <row r="169" customFormat="1" s="3">
+      <c r="A169" s="3" t="inlineStr">
         <is>
           <t>4.4.1</t>
         </is>
       </c>
-      <c r="B169" s="36" t="inlineStr">
+      <c r="B169" s="3" t="inlineStr">
         <is>
           <t>Embankment / associative</t>
         </is>
       </c>
-      <c r="C169" s="36" t="inlineStr">
+      <c r="C169" s="3" t="inlineStr">
         <is>
           <t>1_embankment</t>
         </is>
       </c>
-      <c r="E169" s="36" t="inlineStr">
+      <c r="E169" s="3" t="inlineStr">
         <is>
           <t>L 23, L 24</t>
         </is>
       </c>
-      <c r="F169" s="36" t="inlineStr">
+      <c r="F169" s="3" t="inlineStr">
         <is>
           <t>MohrCoulombClassic</t>
         </is>
       </c>
-      <c r="G169" s="36" t="n">
+      <c r="G169" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="H169" s="36" t="n">
+      <c r="H169" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="K169" s="36" t="n">
+      <c r="K169" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="L169" s="36" t="n">
+      <c r="L169" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="P169" s="38" t="n"/>
-    </row>
-    <row r="170" customFormat="1" s="32">
-      <c r="A170" s="32" t="inlineStr">
+      <c r="P169" s="4" t="n"/>
+    </row>
+    <row r="170" customFormat="1" s="5">
+      <c r="A170" s="5" t="inlineStr">
         <is>
           <t>4.4.1</t>
         </is>
       </c>
-      <c r="B170" s="32" t="inlineStr">
+      <c r="B170" s="5" t="inlineStr">
         <is>
           <t>Sand fill / associative</t>
         </is>
       </c>
-      <c r="C170" s="32" t="inlineStr">
+      <c r="C170" s="5" t="inlineStr">
         <is>
           <t>2_sand_fill</t>
         </is>
       </c>
-      <c r="D170" s="32" t="inlineStr">
+      <c r="D170" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 23, L 22, L 19, L 20</t>
         </is>
       </c>
-      <c r="E170" s="32" t="inlineStr">
+      <c r="E170" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 20, L 25</t>
         </is>
       </c>
-      <c r="F170" s="32" t="inlineStr">
+      <c r="F170" s="5" t="inlineStr">
         <is>
           <t>MohrCoulombClassic</t>
         </is>
       </c>
-      <c r="G170" s="32" t="n">
+      <c r="G170" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="H170" s="32" t="n">
+      <c r="H170" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="K170" s="32" t="n">
+      <c r="K170" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="L170" s="32" t="n">
+      <c r="L170" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="P170" s="34" t="n"/>
+      <c r="P170" s="6" t="n"/>
     </row>
     <row r="171" customFormat="1" s="8">
       <c r="A171" s="8" t="inlineStr">
@@ -11972,96 +11975,96 @@
         <v>48.51</v>
       </c>
     </row>
-    <row r="186" customFormat="1" s="36">
-      <c r="A186" s="36" t="inlineStr">
+    <row r="186" customFormat="1" s="3">
+      <c r="A186" s="3" t="inlineStr">
         <is>
           <t>4.0.2</t>
         </is>
       </c>
-      <c r="B186" s="36" t="inlineStr">
+      <c r="B186" s="3" t="inlineStr">
         <is>
           <t>Embankment / non-associative</t>
         </is>
       </c>
-      <c r="C186" s="36" t="inlineStr">
+      <c r="C186" s="3" t="inlineStr">
         <is>
           <t>1_embankment</t>
         </is>
       </c>
-      <c r="E186" s="36" t="inlineStr">
+      <c r="E186" s="3" t="inlineStr">
         <is>
           <t>L 23, L 24</t>
         </is>
       </c>
-      <c r="F186" s="37" t="inlineStr">
+      <c r="F186" s="7" t="inlineStr">
         <is>
           <t>MohrCoulombAdvanced</t>
         </is>
       </c>
-      <c r="G186" s="36" t="n">
+      <c r="G186" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="H186" s="36" t="n">
+      <c r="H186" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="K186" s="37" t="n">
+      <c r="K186" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="L186" s="37" t="n">
+      <c r="L186" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="M186" s="37" t="n">
+      <c r="M186" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="P186" s="38" t="n"/>
-    </row>
-    <row r="187" customFormat="1" s="32">
-      <c r="A187" s="32" t="inlineStr">
+      <c r="P186" s="4" t="n"/>
+    </row>
+    <row r="187" customFormat="1" s="5">
+      <c r="A187" s="5" t="inlineStr">
         <is>
           <t>4.0.2</t>
         </is>
       </c>
-      <c r="B187" s="32" t="inlineStr">
+      <c r="B187" s="5" t="inlineStr">
         <is>
           <t>Sand fill / non-associative</t>
         </is>
       </c>
-      <c r="C187" s="32" t="inlineStr">
+      <c r="C187" s="5" t="inlineStr">
         <is>
           <t>2_sand_fill</t>
         </is>
       </c>
-      <c r="D187" s="32" t="inlineStr">
+      <c r="D187" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 23, L 22, L 19, L 20</t>
         </is>
       </c>
-      <c r="E187" s="32" t="inlineStr">
+      <c r="E187" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 20, L 25</t>
         </is>
       </c>
-      <c r="F187" s="33" t="inlineStr">
+      <c r="F187" s="30" t="inlineStr">
         <is>
           <t>MohrCoulombAdvanced</t>
         </is>
       </c>
-      <c r="G187" s="32" t="n">
+      <c r="G187" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="H187" s="32" t="n">
+      <c r="H187" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="K187" s="33" t="n">
+      <c r="K187" s="30" t="n">
         <v>36</v>
       </c>
-      <c r="L187" s="33" t="n">
+      <c r="L187" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="M187" s="33" t="n">
+      <c r="M187" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="P187" s="34" t="n"/>
+      <c r="P187" s="6" t="n"/>
     </row>
     <row r="188" customFormat="1" s="8">
       <c r="A188" s="8" t="inlineStr">
@@ -12878,96 +12881,96 @@
         </is>
       </c>
     </row>
-    <row r="203" customFormat="1" s="36">
-      <c r="A203" s="36" t="inlineStr">
+    <row r="203" customFormat="1" s="3">
+      <c r="A203" s="3" t="inlineStr">
         <is>
           <t>4.4.2</t>
         </is>
       </c>
-      <c r="B203" s="36" t="inlineStr">
+      <c r="B203" s="3" t="inlineStr">
         <is>
           <t>Embankment / non-associative</t>
         </is>
       </c>
-      <c r="C203" s="36" t="inlineStr">
+      <c r="C203" s="3" t="inlineStr">
         <is>
           <t>1_embankment</t>
         </is>
       </c>
-      <c r="E203" s="36" t="inlineStr">
+      <c r="E203" s="3" t="inlineStr">
         <is>
           <t>L 23, L 24</t>
         </is>
       </c>
-      <c r="F203" s="37" t="inlineStr">
+      <c r="F203" s="7" t="inlineStr">
         <is>
           <t>MohrCoulombAdvanced</t>
         </is>
       </c>
-      <c r="G203" s="36" t="n">
+      <c r="G203" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="H203" s="36" t="n">
+      <c r="H203" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="K203" s="37" t="n">
+      <c r="K203" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="L203" s="37" t="n">
+      <c r="L203" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="M203" s="37" t="n">
+      <c r="M203" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="P203" s="38" t="n"/>
-    </row>
-    <row r="204" customFormat="1" s="32">
-      <c r="A204" s="32" t="inlineStr">
+      <c r="P203" s="4" t="n"/>
+    </row>
+    <row r="204" customFormat="1" s="5">
+      <c r="A204" s="5" t="inlineStr">
         <is>
           <t>4.4.2</t>
         </is>
       </c>
-      <c r="B204" s="32" t="inlineStr">
+      <c r="B204" s="5" t="inlineStr">
         <is>
           <t>Sand fill / non-associative</t>
         </is>
       </c>
-      <c r="C204" s="32" t="inlineStr">
+      <c r="C204" s="5" t="inlineStr">
         <is>
           <t>2_sand_fill</t>
         </is>
       </c>
-      <c r="D204" s="32" t="inlineStr">
+      <c r="D204" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 23, L 22, L 19, L 20</t>
         </is>
       </c>
-      <c r="E204" s="32" t="inlineStr">
+      <c r="E204" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 20, L 25</t>
         </is>
       </c>
-      <c r="F204" s="33" t="inlineStr">
+      <c r="F204" s="30" t="inlineStr">
         <is>
           <t>MohrCoulombAdvanced</t>
         </is>
       </c>
-      <c r="G204" s="32" t="n">
+      <c r="G204" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="H204" s="32" t="n">
+      <c r="H204" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="K204" s="33" t="n">
+      <c r="K204" s="30" t="n">
         <v>36</v>
       </c>
-      <c r="L204" s="33" t="n">
+      <c r="L204" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="M204" s="33" t="n">
+      <c r="M204" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="P204" s="34" t="n"/>
+      <c r="P204" s="6" t="n"/>
     </row>
     <row r="205" customFormat="1" s="8">
       <c r="A205" s="8" t="inlineStr">
@@ -15358,90 +15361,90 @@
         <v>25</v>
       </c>
     </row>
-    <row r="250" customFormat="1" s="36">
-      <c r="A250" s="36" t="inlineStr">
+    <row r="250" customFormat="1" s="3">
+      <c r="A250" s="3" t="inlineStr">
         <is>
           <t>5.0.1</t>
         </is>
       </c>
-      <c r="B250" s="36" t="inlineStr">
+      <c r="B250" s="3" t="inlineStr">
         <is>
           <t>Embankment / associative</t>
         </is>
       </c>
-      <c r="C250" s="36" t="inlineStr">
+      <c r="C250" s="3" t="inlineStr">
         <is>
           <t>1_embankment</t>
         </is>
       </c>
-      <c r="E250" s="36" t="inlineStr">
+      <c r="E250" s="3" t="inlineStr">
         <is>
           <t>L 23, L 24</t>
         </is>
       </c>
-      <c r="F250" s="36" t="inlineStr">
+      <c r="F250" s="3" t="inlineStr">
         <is>
           <t>MohrCoulombClassic</t>
         </is>
       </c>
-      <c r="G250" s="36" t="n">
+      <c r="G250" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="H250" s="36" t="n">
+      <c r="H250" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="K250" s="36" t="n">
+      <c r="K250" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="L250" s="36" t="n">
+      <c r="L250" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="P250" s="38" t="n"/>
-    </row>
-    <row r="251" customFormat="1" s="32">
-      <c r="A251" s="32" t="inlineStr">
+      <c r="P250" s="4" t="n"/>
+    </row>
+    <row r="251" customFormat="1" s="5">
+      <c r="A251" s="5" t="inlineStr">
         <is>
           <t>5.0.1</t>
         </is>
       </c>
-      <c r="B251" s="32" t="inlineStr">
+      <c r="B251" s="5" t="inlineStr">
         <is>
           <t>Sand fill / associative</t>
         </is>
       </c>
-      <c r="C251" s="32" t="inlineStr">
+      <c r="C251" s="5" t="inlineStr">
         <is>
           <t>2_sand_fill</t>
         </is>
       </c>
-      <c r="D251" s="32" t="inlineStr">
+      <c r="D251" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 23, L 22, L 19, L 20</t>
         </is>
       </c>
-      <c r="E251" s="32" t="inlineStr">
+      <c r="E251" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 20, L 25</t>
         </is>
       </c>
-      <c r="F251" s="32" t="inlineStr">
+      <c r="F251" s="5" t="inlineStr">
         <is>
           <t>MohrCoulombClassic</t>
         </is>
       </c>
-      <c r="G251" s="32" t="n">
+      <c r="G251" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="H251" s="32" t="n">
+      <c r="H251" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="K251" s="32" t="n">
+      <c r="K251" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="L251" s="32" t="n">
+      <c r="L251" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="P251" s="34" t="n"/>
+      <c r="P251" s="6" t="n"/>
     </row>
     <row r="252" customFormat="1" s="8">
       <c r="A252" s="8" t="inlineStr">
@@ -16258,90 +16261,90 @@
         </is>
       </c>
     </row>
-    <row r="267" customFormat="1" s="36">
-      <c r="A267" s="36" t="inlineStr">
+    <row r="267" customFormat="1" s="3">
+      <c r="A267" s="3" t="inlineStr">
         <is>
           <t>5.5.1</t>
         </is>
       </c>
-      <c r="B267" s="36" t="inlineStr">
+      <c r="B267" s="3" t="inlineStr">
         <is>
           <t>Embankment / associative</t>
         </is>
       </c>
-      <c r="C267" s="36" t="inlineStr">
+      <c r="C267" s="3" t="inlineStr">
         <is>
           <t>1_embankment</t>
         </is>
       </c>
-      <c r="E267" s="36" t="inlineStr">
+      <c r="E267" s="3" t="inlineStr">
         <is>
           <t>L 23, L 24</t>
         </is>
       </c>
-      <c r="F267" s="36" t="inlineStr">
+      <c r="F267" s="3" t="inlineStr">
         <is>
           <t>MohrCoulombClassic</t>
         </is>
       </c>
-      <c r="G267" s="36" t="n">
+      <c r="G267" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="H267" s="36" t="n">
+      <c r="H267" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="K267" s="36" t="n">
+      <c r="K267" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="L267" s="36" t="n">
+      <c r="L267" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="P267" s="38" t="n"/>
-    </row>
-    <row r="268" customFormat="1" s="32">
-      <c r="A268" s="32" t="inlineStr">
+      <c r="P267" s="4" t="n"/>
+    </row>
+    <row r="268" customFormat="1" s="5">
+      <c r="A268" s="5" t="inlineStr">
         <is>
           <t>5.5.1</t>
         </is>
       </c>
-      <c r="B268" s="32" t="inlineStr">
+      <c r="B268" s="5" t="inlineStr">
         <is>
           <t>Sand fill / associative</t>
         </is>
       </c>
-      <c r="C268" s="32" t="inlineStr">
+      <c r="C268" s="5" t="inlineStr">
         <is>
           <t>2_sand_fill</t>
         </is>
       </c>
-      <c r="D268" s="32" t="inlineStr">
+      <c r="D268" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 23, L 22, L 19, L 20</t>
         </is>
       </c>
-      <c r="E268" s="32" t="inlineStr">
+      <c r="E268" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 20, L 25</t>
         </is>
       </c>
-      <c r="F268" s="32" t="inlineStr">
+      <c r="F268" s="5" t="inlineStr">
         <is>
           <t>MohrCoulombClassic</t>
         </is>
       </c>
-      <c r="G268" s="32" t="n">
+      <c r="G268" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="H268" s="32" t="n">
+      <c r="H268" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="K268" s="32" t="n">
+      <c r="K268" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="L268" s="32" t="n">
+      <c r="L268" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="P268" s="34" t="n"/>
+      <c r="P268" s="6" t="n"/>
     </row>
     <row r="269" customFormat="1" s="8">
       <c r="A269" s="8" t="inlineStr">
@@ -17130,96 +17133,96 @@
         <v>25</v>
       </c>
     </row>
-    <row r="284" customFormat="1" s="36">
-      <c r="A284" s="36" t="inlineStr">
+    <row r="284" customFormat="1" s="3">
+      <c r="A284" s="3" t="inlineStr">
         <is>
           <t>5.0.2</t>
         </is>
       </c>
-      <c r="B284" s="36" t="inlineStr">
+      <c r="B284" s="3" t="inlineStr">
         <is>
           <t>Embankment / non-associative</t>
         </is>
       </c>
-      <c r="C284" s="36" t="inlineStr">
+      <c r="C284" s="3" t="inlineStr">
         <is>
           <t>1_embankment</t>
         </is>
       </c>
-      <c r="E284" s="36" t="inlineStr">
+      <c r="E284" s="3" t="inlineStr">
         <is>
           <t>L 23, L 24</t>
         </is>
       </c>
-      <c r="F284" s="37" t="inlineStr">
+      <c r="F284" s="7" t="inlineStr">
         <is>
           <t>MohrCoulombAdvanced</t>
         </is>
       </c>
-      <c r="G284" s="36" t="n">
+      <c r="G284" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="H284" s="36" t="n">
+      <c r="H284" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="K284" s="37" t="n">
+      <c r="K284" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="L284" s="37" t="n">
+      <c r="L284" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="M284" s="37" t="n">
+      <c r="M284" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="P284" s="38" t="n"/>
-    </row>
-    <row r="285" customFormat="1" s="32">
-      <c r="A285" s="32" t="inlineStr">
+      <c r="P284" s="4" t="n"/>
+    </row>
+    <row r="285" customFormat="1" s="5">
+      <c r="A285" s="5" t="inlineStr">
         <is>
           <t>5.0.2</t>
         </is>
       </c>
-      <c r="B285" s="32" t="inlineStr">
+      <c r="B285" s="5" t="inlineStr">
         <is>
           <t>Sand fill / non-associative</t>
         </is>
       </c>
-      <c r="C285" s="32" t="inlineStr">
+      <c r="C285" s="5" t="inlineStr">
         <is>
           <t>2_sand_fill</t>
         </is>
       </c>
-      <c r="D285" s="32" t="inlineStr">
+      <c r="D285" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 23, L 22, L 19, L 20</t>
         </is>
       </c>
-      <c r="E285" s="32" t="inlineStr">
+      <c r="E285" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 20, L 25</t>
         </is>
       </c>
-      <c r="F285" s="33" t="inlineStr">
+      <c r="F285" s="30" t="inlineStr">
         <is>
           <t>MohrCoulombAdvanced</t>
         </is>
       </c>
-      <c r="G285" s="32" t="n">
+      <c r="G285" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="H285" s="32" t="n">
+      <c r="H285" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="K285" s="33" t="n">
+      <c r="K285" s="30" t="n">
         <v>36</v>
       </c>
-      <c r="L285" s="33" t="n">
+      <c r="L285" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="M285" s="33" t="n">
+      <c r="M285" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="P285" s="34" t="n"/>
+      <c r="P285" s="6" t="n"/>
     </row>
     <row r="286" customFormat="1" s="8">
       <c r="A286" s="8" t="inlineStr">
@@ -18036,96 +18039,96 @@
         </is>
       </c>
     </row>
-    <row r="301" customFormat="1" s="36">
-      <c r="A301" s="36" t="inlineStr">
+    <row r="301" customFormat="1" s="3">
+      <c r="A301" s="3" t="inlineStr">
         <is>
           <t>5.5.2</t>
         </is>
       </c>
-      <c r="B301" s="36" t="inlineStr">
+      <c r="B301" s="3" t="inlineStr">
         <is>
           <t>Embankment / non-associative</t>
         </is>
       </c>
-      <c r="C301" s="36" t="inlineStr">
+      <c r="C301" s="3" t="inlineStr">
         <is>
           <t>1_embankment</t>
         </is>
       </c>
-      <c r="E301" s="36" t="inlineStr">
+      <c r="E301" s="3" t="inlineStr">
         <is>
           <t>L 23, L 24</t>
         </is>
       </c>
-      <c r="F301" s="37" t="inlineStr">
+      <c r="F301" s="7" t="inlineStr">
         <is>
           <t>MohrCoulombAdvanced</t>
         </is>
       </c>
-      <c r="G301" s="36" t="n">
+      <c r="G301" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="H301" s="36" t="n">
+      <c r="H301" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="K301" s="37" t="n">
+      <c r="K301" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="L301" s="37" t="n">
+      <c r="L301" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="M301" s="37" t="n">
+      <c r="M301" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="P301" s="38" t="n"/>
-    </row>
-    <row r="302" customFormat="1" s="32">
-      <c r="A302" s="32" t="inlineStr">
+      <c r="P301" s="4" t="n"/>
+    </row>
+    <row r="302" customFormat="1" s="5">
+      <c r="A302" s="5" t="inlineStr">
         <is>
           <t>5.5.2</t>
         </is>
       </c>
-      <c r="B302" s="32" t="inlineStr">
+      <c r="B302" s="5" t="inlineStr">
         <is>
           <t>Sand fill / non-associative</t>
         </is>
       </c>
-      <c r="C302" s="32" t="inlineStr">
+      <c r="C302" s="5" t="inlineStr">
         <is>
           <t>2_sand_fill</t>
         </is>
       </c>
-      <c r="D302" s="32" t="inlineStr">
+      <c r="D302" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 23, L 22, L 19, L 20</t>
         </is>
       </c>
-      <c r="E302" s="32" t="inlineStr">
+      <c r="E302" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 20, L 25</t>
         </is>
       </c>
-      <c r="F302" s="33" t="inlineStr">
+      <c r="F302" s="30" t="inlineStr">
         <is>
           <t>MohrCoulombAdvanced</t>
         </is>
       </c>
-      <c r="G302" s="32" t="n">
+      <c r="G302" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="H302" s="32" t="n">
+      <c r="H302" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="K302" s="33" t="n">
+      <c r="K302" s="30" t="n">
         <v>36</v>
       </c>
-      <c r="L302" s="33" t="n">
+      <c r="L302" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="M302" s="33" t="n">
+      <c r="M302" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="P302" s="34" t="n"/>
+      <c r="P302" s="6" t="n"/>
     </row>
     <row r="303" customFormat="1" s="8">
       <c r="A303" s="8" t="inlineStr">
@@ -20516,90 +20519,90 @@
         <v>25</v>
       </c>
     </row>
-    <row r="348" customFormat="1" s="36">
-      <c r="A348" s="36" t="inlineStr">
+    <row r="348" customFormat="1" s="3">
+      <c r="A348" s="3" t="inlineStr">
         <is>
           <t>10.0.1</t>
         </is>
       </c>
-      <c r="B348" s="36" t="inlineStr">
+      <c r="B348" s="3" t="inlineStr">
         <is>
           <t>Embankment / associative</t>
         </is>
       </c>
-      <c r="C348" s="36" t="inlineStr">
+      <c r="C348" s="3" t="inlineStr">
         <is>
           <t>1_embankment</t>
         </is>
       </c>
-      <c r="E348" s="36" t="inlineStr">
+      <c r="E348" s="3" t="inlineStr">
         <is>
           <t>L 23, L 24</t>
         </is>
       </c>
-      <c r="F348" s="36" t="inlineStr">
+      <c r="F348" s="3" t="inlineStr">
         <is>
           <t>MohrCoulombClassic</t>
         </is>
       </c>
-      <c r="G348" s="36" t="n">
+      <c r="G348" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="H348" s="36" t="n">
+      <c r="H348" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="K348" s="36" t="n">
+      <c r="K348" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="L348" s="36" t="n">
+      <c r="L348" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="P348" s="38" t="n"/>
-    </row>
-    <row r="349" customFormat="1" s="32">
-      <c r="A349" s="32" t="inlineStr">
+      <c r="P348" s="4" t="n"/>
+    </row>
+    <row r="349" customFormat="1" s="5">
+      <c r="A349" s="5" t="inlineStr">
         <is>
           <t>10.0.1</t>
         </is>
       </c>
-      <c r="B349" s="32" t="inlineStr">
+      <c r="B349" s="5" t="inlineStr">
         <is>
           <t>Sand fill / associative</t>
         </is>
       </c>
-      <c r="C349" s="32" t="inlineStr">
+      <c r="C349" s="5" t="inlineStr">
         <is>
           <t>2_sand_fill</t>
         </is>
       </c>
-      <c r="D349" s="32" t="inlineStr">
+      <c r="D349" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 23, L 22, L 19, L 20</t>
         </is>
       </c>
-      <c r="E349" s="32" t="inlineStr">
+      <c r="E349" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 20, L 25</t>
         </is>
       </c>
-      <c r="F349" s="32" t="inlineStr">
+      <c r="F349" s="5" t="inlineStr">
         <is>
           <t>MohrCoulombClassic</t>
         </is>
       </c>
-      <c r="G349" s="32" t="n">
+      <c r="G349" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="H349" s="32" t="n">
+      <c r="H349" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="K349" s="32" t="n">
+      <c r="K349" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="L349" s="32" t="n">
+      <c r="L349" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="P349" s="34" t="n"/>
+      <c r="P349" s="6" t="n"/>
     </row>
     <row r="350" customFormat="1" s="8">
       <c r="A350" s="8" t="inlineStr">
@@ -21416,90 +21419,90 @@
         </is>
       </c>
     </row>
-    <row r="365" customFormat="1" s="36">
-      <c r="A365" s="36" t="inlineStr">
+    <row r="365" customFormat="1" s="3">
+      <c r="A365" s="3" t="inlineStr">
         <is>
           <t>10.10.1</t>
         </is>
       </c>
-      <c r="B365" s="36" t="inlineStr">
+      <c r="B365" s="3" t="inlineStr">
         <is>
           <t>Embankment / associative</t>
         </is>
       </c>
-      <c r="C365" s="36" t="inlineStr">
+      <c r="C365" s="3" t="inlineStr">
         <is>
           <t>1_embankment</t>
         </is>
       </c>
-      <c r="E365" s="36" t="inlineStr">
+      <c r="E365" s="3" t="inlineStr">
         <is>
           <t>L 23, L 24</t>
         </is>
       </c>
-      <c r="F365" s="36" t="inlineStr">
+      <c r="F365" s="3" t="inlineStr">
         <is>
           <t>MohrCoulombClassic</t>
         </is>
       </c>
-      <c r="G365" s="36" t="n">
+      <c r="G365" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="H365" s="36" t="n">
+      <c r="H365" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="K365" s="36" t="n">
+      <c r="K365" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="L365" s="36" t="n">
+      <c r="L365" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="P365" s="38" t="n"/>
-    </row>
-    <row r="366" customFormat="1" s="32">
-      <c r="A366" s="32" t="inlineStr">
+      <c r="P365" s="4" t="n"/>
+    </row>
+    <row r="366" customFormat="1" s="5">
+      <c r="A366" s="5" t="inlineStr">
         <is>
           <t>10.10.1</t>
         </is>
       </c>
-      <c r="B366" s="32" t="inlineStr">
+      <c r="B366" s="5" t="inlineStr">
         <is>
           <t>Sand fill / associative</t>
         </is>
       </c>
-      <c r="C366" s="32" t="inlineStr">
+      <c r="C366" s="5" t="inlineStr">
         <is>
           <t>2_sand_fill</t>
         </is>
       </c>
-      <c r="D366" s="32" t="inlineStr">
+      <c r="D366" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 23, L 22, L 19, L 20</t>
         </is>
       </c>
-      <c r="E366" s="32" t="inlineStr">
+      <c r="E366" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 20, L 25</t>
         </is>
       </c>
-      <c r="F366" s="32" t="inlineStr">
+      <c r="F366" s="5" t="inlineStr">
         <is>
           <t>MohrCoulombClassic</t>
         </is>
       </c>
-      <c r="G366" s="32" t="n">
+      <c r="G366" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="H366" s="32" t="n">
+      <c r="H366" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="K366" s="32" t="n">
+      <c r="K366" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="L366" s="32" t="n">
+      <c r="L366" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="P366" s="34" t="n"/>
+      <c r="P366" s="6" t="n"/>
     </row>
     <row r="367" customFormat="1" s="8">
       <c r="A367" s="8" t="inlineStr">
@@ -22288,96 +22291,96 @@
         <v>25</v>
       </c>
     </row>
-    <row r="382" customFormat="1" s="36">
-      <c r="A382" s="36" t="inlineStr">
+    <row r="382" customFormat="1" s="3">
+      <c r="A382" s="3" t="inlineStr">
         <is>
           <t>10.0.2</t>
         </is>
       </c>
-      <c r="B382" s="36" t="inlineStr">
+      <c r="B382" s="3" t="inlineStr">
         <is>
           <t>Embankment / non-associative</t>
         </is>
       </c>
-      <c r="C382" s="36" t="inlineStr">
+      <c r="C382" s="3" t="inlineStr">
         <is>
           <t>1_embankment</t>
         </is>
       </c>
-      <c r="E382" s="36" t="inlineStr">
+      <c r="E382" s="3" t="inlineStr">
         <is>
           <t>L 23, L 24</t>
         </is>
       </c>
-      <c r="F382" s="37" t="inlineStr">
+      <c r="F382" s="7" t="inlineStr">
         <is>
           <t>MohrCoulombAdvanced</t>
         </is>
       </c>
-      <c r="G382" s="36" t="n">
+      <c r="G382" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="H382" s="36" t="n">
+      <c r="H382" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="K382" s="37" t="n">
+      <c r="K382" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="L382" s="37" t="n">
+      <c r="L382" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="M382" s="37" t="n">
+      <c r="M382" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="P382" s="38" t="n"/>
-    </row>
-    <row r="383" customFormat="1" s="32">
-      <c r="A383" s="32" t="inlineStr">
+      <c r="P382" s="4" t="n"/>
+    </row>
+    <row r="383" customFormat="1" s="5">
+      <c r="A383" s="5" t="inlineStr">
         <is>
           <t>10.0.2</t>
         </is>
       </c>
-      <c r="B383" s="32" t="inlineStr">
+      <c r="B383" s="5" t="inlineStr">
         <is>
           <t>Sand fill / non-associative</t>
         </is>
       </c>
-      <c r="C383" s="32" t="inlineStr">
+      <c r="C383" s="5" t="inlineStr">
         <is>
           <t>2_sand_fill</t>
         </is>
       </c>
-      <c r="D383" s="32" t="inlineStr">
+      <c r="D383" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 23, L 22, L 19, L 20</t>
         </is>
       </c>
-      <c r="E383" s="32" t="inlineStr">
+      <c r="E383" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 20, L 25</t>
         </is>
       </c>
-      <c r="F383" s="33" t="inlineStr">
+      <c r="F383" s="30" t="inlineStr">
         <is>
           <t>MohrCoulombAdvanced</t>
         </is>
       </c>
-      <c r="G383" s="32" t="n">
+      <c r="G383" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="H383" s="32" t="n">
+      <c r="H383" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="K383" s="33" t="n">
+      <c r="K383" s="30" t="n">
         <v>36</v>
       </c>
-      <c r="L383" s="33" t="n">
+      <c r="L383" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="M383" s="33" t="n">
+      <c r="M383" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="P383" s="34" t="n"/>
+      <c r="P383" s="6" t="n"/>
     </row>
     <row r="384" customFormat="1" s="8">
       <c r="A384" s="8" t="inlineStr">
@@ -23194,96 +23197,96 @@
         </is>
       </c>
     </row>
-    <row r="399" customFormat="1" s="36">
-      <c r="A399" s="36" t="inlineStr">
+    <row r="399" customFormat="1" s="3">
+      <c r="A399" s="3" t="inlineStr">
         <is>
           <t>10.10.2</t>
         </is>
       </c>
-      <c r="B399" s="36" t="inlineStr">
+      <c r="B399" s="3" t="inlineStr">
         <is>
           <t>Embankment / non-associative</t>
         </is>
       </c>
-      <c r="C399" s="36" t="inlineStr">
+      <c r="C399" s="3" t="inlineStr">
         <is>
           <t>1_embankment</t>
         </is>
       </c>
-      <c r="E399" s="36" t="inlineStr">
+      <c r="E399" s="3" t="inlineStr">
         <is>
           <t>L 23, L 24</t>
         </is>
       </c>
-      <c r="F399" s="37" t="inlineStr">
+      <c r="F399" s="7" t="inlineStr">
         <is>
           <t>MohrCoulombAdvanced</t>
         </is>
       </c>
-      <c r="G399" s="36" t="n">
+      <c r="G399" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="H399" s="36" t="n">
+      <c r="H399" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="K399" s="37" t="n">
+      <c r="K399" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="L399" s="37" t="n">
+      <c r="L399" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="M399" s="37" t="n">
+      <c r="M399" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="P399" s="38" t="n"/>
-    </row>
-    <row r="400" customFormat="1" s="32">
-      <c r="A400" s="32" t="inlineStr">
+      <c r="P399" s="4" t="n"/>
+    </row>
+    <row r="400" customFormat="1" s="5">
+      <c r="A400" s="5" t="inlineStr">
         <is>
           <t>10.10.2</t>
         </is>
       </c>
-      <c r="B400" s="32" t="inlineStr">
+      <c r="B400" s="5" t="inlineStr">
         <is>
           <t>Sand fill / non-associative</t>
         </is>
       </c>
-      <c r="C400" s="32" t="inlineStr">
+      <c r="C400" s="5" t="inlineStr">
         <is>
           <t>2_sand_fill</t>
         </is>
       </c>
-      <c r="D400" s="32" t="inlineStr">
+      <c r="D400" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 23, L 22, L 19, L 20</t>
         </is>
       </c>
-      <c r="E400" s="32" t="inlineStr">
+      <c r="E400" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 20, L 25</t>
         </is>
       </c>
-      <c r="F400" s="33" t="inlineStr">
+      <c r="F400" s="30" t="inlineStr">
         <is>
           <t>MohrCoulombAdvanced</t>
         </is>
       </c>
-      <c r="G400" s="32" t="n">
+      <c r="G400" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="H400" s="32" t="n">
+      <c r="H400" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="K400" s="33" t="n">
+      <c r="K400" s="30" t="n">
         <v>36</v>
       </c>
-      <c r="L400" s="33" t="n">
+      <c r="L400" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="M400" s="33" t="n">
+      <c r="M400" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="P400" s="34" t="n"/>
+      <c r="P400" s="6" t="n"/>
     </row>
     <row r="401" customFormat="1" s="8">
       <c r="A401" s="8" t="inlineStr">
@@ -25674,90 +25677,90 @@
         <v>25</v>
       </c>
     </row>
-    <row r="446" customFormat="1" s="36">
-      <c r="A446" s="36" t="inlineStr">
+    <row r="446" customFormat="1" s="3">
+      <c r="A446" s="3" t="inlineStr">
         <is>
           <t>11.0.1</t>
         </is>
       </c>
-      <c r="B446" s="36" t="inlineStr">
+      <c r="B446" s="3" t="inlineStr">
         <is>
           <t>Embankment / associative</t>
         </is>
       </c>
-      <c r="C446" s="36" t="inlineStr">
+      <c r="C446" s="3" t="inlineStr">
         <is>
           <t>1_embankment</t>
         </is>
       </c>
-      <c r="E446" s="36" t="inlineStr">
+      <c r="E446" s="3" t="inlineStr">
         <is>
           <t>L 23, L 24</t>
         </is>
       </c>
-      <c r="F446" s="36" t="inlineStr">
+      <c r="F446" s="3" t="inlineStr">
         <is>
           <t>MohrCoulombClassic</t>
         </is>
       </c>
-      <c r="G446" s="36" t="n">
+      <c r="G446" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="H446" s="36" t="n">
+      <c r="H446" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="K446" s="36" t="n">
+      <c r="K446" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="L446" s="36" t="n">
+      <c r="L446" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="P446" s="38" t="n"/>
-    </row>
-    <row r="447" customFormat="1" s="32">
-      <c r="A447" s="32" t="inlineStr">
+      <c r="P446" s="4" t="n"/>
+    </row>
+    <row r="447" customFormat="1" s="5">
+      <c r="A447" s="5" t="inlineStr">
         <is>
           <t>11.0.1</t>
         </is>
       </c>
-      <c r="B447" s="32" t="inlineStr">
+      <c r="B447" s="5" t="inlineStr">
         <is>
           <t>Sand fill / associative</t>
         </is>
       </c>
-      <c r="C447" s="32" t="inlineStr">
+      <c r="C447" s="5" t="inlineStr">
         <is>
           <t>2_sand_fill</t>
         </is>
       </c>
-      <c r="D447" s="32" t="inlineStr">
+      <c r="D447" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 23, L 22, L 19, L 20</t>
         </is>
       </c>
-      <c r="E447" s="32" t="inlineStr">
+      <c r="E447" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 20, L 25</t>
         </is>
       </c>
-      <c r="F447" s="32" t="inlineStr">
+      <c r="F447" s="5" t="inlineStr">
         <is>
           <t>MohrCoulombClassic</t>
         </is>
       </c>
-      <c r="G447" s="32" t="n">
+      <c r="G447" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="H447" s="32" t="n">
+      <c r="H447" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="K447" s="32" t="n">
+      <c r="K447" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="L447" s="32" t="n">
+      <c r="L447" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="P447" s="34" t="n"/>
+      <c r="P447" s="6" t="n"/>
     </row>
     <row r="448" customFormat="1" s="8">
       <c r="A448" s="8" t="inlineStr">
@@ -26574,90 +26577,90 @@
         </is>
       </c>
     </row>
-    <row r="463" customFormat="1" s="36">
-      <c r="A463" s="36" t="inlineStr">
+    <row r="463" customFormat="1" s="3">
+      <c r="A463" s="3" t="inlineStr">
         <is>
           <t>11.11.1</t>
         </is>
       </c>
-      <c r="B463" s="36" t="inlineStr">
+      <c r="B463" s="3" t="inlineStr">
         <is>
           <t>Embankment / associative</t>
         </is>
       </c>
-      <c r="C463" s="36" t="inlineStr">
+      <c r="C463" s="3" t="inlineStr">
         <is>
           <t>1_embankment</t>
         </is>
       </c>
-      <c r="E463" s="36" t="inlineStr">
+      <c r="E463" s="3" t="inlineStr">
         <is>
           <t>L 23, L 24</t>
         </is>
       </c>
-      <c r="F463" s="36" t="inlineStr">
+      <c r="F463" s="3" t="inlineStr">
         <is>
           <t>MohrCoulombClassic</t>
         </is>
       </c>
-      <c r="G463" s="36" t="n">
+      <c r="G463" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="H463" s="36" t="n">
+      <c r="H463" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="K463" s="36" t="n">
+      <c r="K463" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="L463" s="36" t="n">
+      <c r="L463" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="P463" s="38" t="n"/>
-    </row>
-    <row r="464" customFormat="1" s="32">
-      <c r="A464" s="32" t="inlineStr">
+      <c r="P463" s="4" t="n"/>
+    </row>
+    <row r="464" customFormat="1" s="5">
+      <c r="A464" s="5" t="inlineStr">
         <is>
           <t>11.11.1</t>
         </is>
       </c>
-      <c r="B464" s="32" t="inlineStr">
+      <c r="B464" s="5" t="inlineStr">
         <is>
           <t>Sand fill / associative</t>
         </is>
       </c>
-      <c r="C464" s="32" t="inlineStr">
+      <c r="C464" s="5" t="inlineStr">
         <is>
           <t>2_sand_fill</t>
         </is>
       </c>
-      <c r="D464" s="32" t="inlineStr">
+      <c r="D464" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 23, L 22, L 19, L 20</t>
         </is>
       </c>
-      <c r="E464" s="32" t="inlineStr">
+      <c r="E464" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 20, L 25</t>
         </is>
       </c>
-      <c r="F464" s="32" t="inlineStr">
+      <c r="F464" s="5" t="inlineStr">
         <is>
           <t>MohrCoulombClassic</t>
         </is>
       </c>
-      <c r="G464" s="32" t="n">
+      <c r="G464" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="H464" s="32" t="n">
+      <c r="H464" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="K464" s="32" t="n">
+      <c r="K464" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="L464" s="32" t="n">
+      <c r="L464" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="P464" s="34" t="n"/>
+      <c r="P464" s="6" t="n"/>
     </row>
     <row r="465" customFormat="1" s="8">
       <c r="A465" s="8" t="inlineStr">
@@ -27446,96 +27449,96 @@
         <v>25</v>
       </c>
     </row>
-    <row r="480" customFormat="1" s="36">
-      <c r="A480" s="36" t="inlineStr">
+    <row r="480" customFormat="1" s="3">
+      <c r="A480" s="3" t="inlineStr">
         <is>
           <t>11.0.2</t>
         </is>
       </c>
-      <c r="B480" s="36" t="inlineStr">
+      <c r="B480" s="3" t="inlineStr">
         <is>
           <t>Embankment / non-associative</t>
         </is>
       </c>
-      <c r="C480" s="36" t="inlineStr">
+      <c r="C480" s="3" t="inlineStr">
         <is>
           <t>1_embankment</t>
         </is>
       </c>
-      <c r="E480" s="36" t="inlineStr">
+      <c r="E480" s="3" t="inlineStr">
         <is>
           <t>L 23, L 24</t>
         </is>
       </c>
-      <c r="F480" s="37" t="inlineStr">
+      <c r="F480" s="7" t="inlineStr">
         <is>
           <t>MohrCoulombAdvanced</t>
         </is>
       </c>
-      <c r="G480" s="36" t="n">
+      <c r="G480" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="H480" s="36" t="n">
+      <c r="H480" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="K480" s="37" t="n">
+      <c r="K480" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="L480" s="37" t="n">
+      <c r="L480" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="M480" s="37" t="n">
+      <c r="M480" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="P480" s="38" t="n"/>
-    </row>
-    <row r="481" customFormat="1" s="32">
-      <c r="A481" s="32" t="inlineStr">
+      <c r="P480" s="4" t="n"/>
+    </row>
+    <row r="481" customFormat="1" s="5">
+      <c r="A481" s="5" t="inlineStr">
         <is>
           <t>11.0.2</t>
         </is>
       </c>
-      <c r="B481" s="32" t="inlineStr">
+      <c r="B481" s="5" t="inlineStr">
         <is>
           <t>Sand fill / non-associative</t>
         </is>
       </c>
-      <c r="C481" s="32" t="inlineStr">
+      <c r="C481" s="5" t="inlineStr">
         <is>
           <t>2_sand_fill</t>
         </is>
       </c>
-      <c r="D481" s="32" t="inlineStr">
+      <c r="D481" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 23, L 22, L 19, L 20</t>
         </is>
       </c>
-      <c r="E481" s="32" t="inlineStr">
+      <c r="E481" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 20, L 25</t>
         </is>
       </c>
-      <c r="F481" s="33" t="inlineStr">
+      <c r="F481" s="30" t="inlineStr">
         <is>
           <t>MohrCoulombAdvanced</t>
         </is>
       </c>
-      <c r="G481" s="32" t="n">
+      <c r="G481" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="H481" s="32" t="n">
+      <c r="H481" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="K481" s="33" t="n">
+      <c r="K481" s="30" t="n">
         <v>36</v>
       </c>
-      <c r="L481" s="33" t="n">
+      <c r="L481" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="M481" s="33" t="n">
+      <c r="M481" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="P481" s="34" t="n"/>
+      <c r="P481" s="6" t="n"/>
     </row>
     <row r="482" customFormat="1" s="8">
       <c r="A482" s="8" t="inlineStr">
@@ -28352,96 +28355,96 @@
         </is>
       </c>
     </row>
-    <row r="497" customFormat="1" s="36">
-      <c r="A497" s="36" t="inlineStr">
+    <row r="497" customFormat="1" s="3">
+      <c r="A497" s="3" t="inlineStr">
         <is>
           <t>11.11.2</t>
         </is>
       </c>
-      <c r="B497" s="36" t="inlineStr">
+      <c r="B497" s="3" t="inlineStr">
         <is>
           <t>Embankment / non-associative</t>
         </is>
       </c>
-      <c r="C497" s="36" t="inlineStr">
+      <c r="C497" s="3" t="inlineStr">
         <is>
           <t>1_embankment</t>
         </is>
       </c>
-      <c r="E497" s="36" t="inlineStr">
+      <c r="E497" s="3" t="inlineStr">
         <is>
           <t>L 23, L 24</t>
         </is>
       </c>
-      <c r="F497" s="37" t="inlineStr">
+      <c r="F497" s="7" t="inlineStr">
         <is>
           <t>MohrCoulombAdvanced</t>
         </is>
       </c>
-      <c r="G497" s="36" t="n">
+      <c r="G497" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="H497" s="36" t="n">
+      <c r="H497" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="K497" s="37" t="n">
+      <c r="K497" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="L497" s="37" t="n">
+      <c r="L497" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="M497" s="37" t="n">
+      <c r="M497" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="P497" s="38" t="n"/>
-    </row>
-    <row r="498" customFormat="1" s="32">
-      <c r="A498" s="32" t="inlineStr">
+      <c r="P497" s="4" t="n"/>
+    </row>
+    <row r="498" customFormat="1" s="5">
+      <c r="A498" s="5" t="inlineStr">
         <is>
           <t>11.11.2</t>
         </is>
       </c>
-      <c r="B498" s="32" t="inlineStr">
+      <c r="B498" s="5" t="inlineStr">
         <is>
           <t>Sand fill / non-associative</t>
         </is>
       </c>
-      <c r="C498" s="32" t="inlineStr">
+      <c r="C498" s="5" t="inlineStr">
         <is>
           <t>2_sand_fill</t>
         </is>
       </c>
-      <c r="D498" s="32" t="inlineStr">
+      <c r="D498" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 23, L 22, L 19, L 20</t>
         </is>
       </c>
-      <c r="E498" s="32" t="inlineStr">
+      <c r="E498" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 20, L 25</t>
         </is>
       </c>
-      <c r="F498" s="33" t="inlineStr">
+      <c r="F498" s="30" t="inlineStr">
         <is>
           <t>MohrCoulombAdvanced</t>
         </is>
       </c>
-      <c r="G498" s="32" t="n">
+      <c r="G498" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="H498" s="32" t="n">
+      <c r="H498" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="K498" s="33" t="n">
+      <c r="K498" s="30" t="n">
         <v>36</v>
       </c>
-      <c r="L498" s="33" t="n">
+      <c r="L498" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="M498" s="33" t="n">
+      <c r="M498" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="P498" s="34" t="n"/>
+      <c r="P498" s="6" t="n"/>
     </row>
     <row r="499" customFormat="1" s="8">
       <c r="A499" s="8" t="inlineStr">
@@ -30862,92 +30865,92 @@
         <v>25</v>
       </c>
     </row>
-    <row r="544" customFormat="1" s="36">
-      <c r="A544" s="36" t="inlineStr">
+    <row r="544" customFormat="1" s="3">
+      <c r="A544" s="3" t="inlineStr">
         <is>
           <t>13.0.1</t>
         </is>
       </c>
-      <c r="B544" s="36" t="inlineStr">
+      <c r="B544" s="3" t="inlineStr">
         <is>
           <t>Embankment / associative+int</t>
         </is>
       </c>
-      <c r="C544" s="36" t="inlineStr">
+      <c r="C544" s="3" t="inlineStr">
         <is>
           <t>1_embankment</t>
         </is>
       </c>
-      <c r="E544" s="36" t="inlineStr">
+      <c r="E544" s="3" t="inlineStr">
         <is>
           <t>L 23, L 24</t>
         </is>
       </c>
-      <c r="F544" s="36" t="inlineStr">
+      <c r="F544" s="3" t="inlineStr">
         <is>
           <t>MohrCoulombClassic</t>
         </is>
       </c>
-      <c r="G544" s="36" t="n">
+      <c r="G544" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="H544" s="36" t="n">
+      <c r="H544" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="K544" s="36">
-        <f>0.38*1.06</f>
+      <c r="K544" s="3">
+        <f>38*1.06</f>
         <v/>
       </c>
-      <c r="L544" s="36" t="n">
+      <c r="L544" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="P544" s="38" t="n"/>
-    </row>
-    <row r="545" customFormat="1" s="32">
-      <c r="A545" s="32" t="inlineStr">
+      <c r="P544" s="4" t="n"/>
+    </row>
+    <row r="545" customFormat="1" s="5">
+      <c r="A545" s="5" t="inlineStr">
         <is>
           <t>13.0.1</t>
         </is>
       </c>
-      <c r="B545" s="32" t="inlineStr">
+      <c r="B545" s="5" t="inlineStr">
         <is>
           <t>Sand fill / associative+int</t>
         </is>
       </c>
-      <c r="C545" s="32" t="inlineStr">
+      <c r="C545" s="5" t="inlineStr">
         <is>
           <t>2_sand_fill</t>
         </is>
       </c>
-      <c r="D545" s="32" t="inlineStr">
+      <c r="D545" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 23, L 22, L 19, L 20</t>
         </is>
       </c>
-      <c r="E545" s="32" t="inlineStr">
+      <c r="E545" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 20, L 25</t>
         </is>
       </c>
-      <c r="F545" s="32" t="inlineStr">
+      <c r="F545" s="5" t="inlineStr">
         <is>
           <t>MohrCoulombClassic</t>
         </is>
       </c>
-      <c r="G545" s="32" t="n">
+      <c r="G545" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="H545" s="32" t="n">
+      <c r="H545" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="K545" s="32">
-        <f>0.36*1.06</f>
+      <c r="K545" s="5">
+        <f>36*1.06</f>
         <v/>
       </c>
-      <c r="L545" s="32" t="n">
+      <c r="L545" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="P545" s="34" t="n"/>
+      <c r="P545" s="6" t="n"/>
     </row>
     <row r="546" customFormat="1" s="8">
       <c r="A546" s="8" t="inlineStr">
@@ -31779,92 +31782,92 @@
         </is>
       </c>
     </row>
-    <row r="561" customFormat="1" s="36">
-      <c r="A561" s="36" t="inlineStr">
+    <row r="561" customFormat="1" s="3">
+      <c r="A561" s="3" t="inlineStr">
         <is>
           <t>13.13.1</t>
         </is>
       </c>
-      <c r="B561" s="36" t="inlineStr">
+      <c r="B561" s="3" t="inlineStr">
         <is>
           <t>Embankment / associative+int</t>
         </is>
       </c>
-      <c r="C561" s="36" t="inlineStr">
+      <c r="C561" s="3" t="inlineStr">
         <is>
           <t>1_embankment</t>
         </is>
       </c>
-      <c r="E561" s="36" t="inlineStr">
+      <c r="E561" s="3" t="inlineStr">
         <is>
           <t>L 23, L 24</t>
         </is>
       </c>
-      <c r="F561" s="36" t="inlineStr">
+      <c r="F561" s="3" t="inlineStr">
         <is>
           <t>MohrCoulombClassic</t>
         </is>
       </c>
-      <c r="G561" s="36" t="n">
+      <c r="G561" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="H561" s="36" t="n">
+      <c r="H561" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="K561" s="36">
-        <f>0.38*1.06</f>
+      <c r="K561" s="3">
+        <f>38*1.06</f>
         <v/>
       </c>
-      <c r="L561" s="36" t="n">
+      <c r="L561" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="P561" s="38" t="n"/>
-    </row>
-    <row r="562" customFormat="1" s="32">
-      <c r="A562" s="32" t="inlineStr">
+      <c r="P561" s="4" t="n"/>
+    </row>
+    <row r="562" customFormat="1" s="5">
+      <c r="A562" s="5" t="inlineStr">
         <is>
           <t>13.13.1</t>
         </is>
       </c>
-      <c r="B562" s="32" t="inlineStr">
+      <c r="B562" s="5" t="inlineStr">
         <is>
           <t>Sand fill / associative+int</t>
         </is>
       </c>
-      <c r="C562" s="32" t="inlineStr">
+      <c r="C562" s="5" t="inlineStr">
         <is>
           <t>2_sand_fill</t>
         </is>
       </c>
-      <c r="D562" s="32" t="inlineStr">
+      <c r="D562" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 23, L 22, L 19, L 20</t>
         </is>
       </c>
-      <c r="E562" s="32" t="inlineStr">
+      <c r="E562" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 20, L 25</t>
         </is>
       </c>
-      <c r="F562" s="32" t="inlineStr">
+      <c r="F562" s="5" t="inlineStr">
         <is>
           <t>MohrCoulombClassic</t>
         </is>
       </c>
-      <c r="G562" s="32" t="n">
+      <c r="G562" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="H562" s="32" t="n">
+      <c r="H562" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="K562" s="32">
-        <f>0.36*1.06</f>
+      <c r="K562" s="5">
+        <f>36*1.06</f>
         <v/>
       </c>
-      <c r="L562" s="32" t="n">
+      <c r="L562" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="P562" s="34" t="n"/>
+      <c r="P562" s="6" t="n"/>
     </row>
     <row r="563" customFormat="1" s="8">
       <c r="A563" s="8" t="inlineStr">
@@ -32668,98 +32671,98 @@
         <v>25</v>
       </c>
     </row>
-    <row r="578" customFormat="1" s="36">
-      <c r="A578" s="36" t="inlineStr">
+    <row r="578" customFormat="1" s="3">
+      <c r="A578" s="3" t="inlineStr">
         <is>
           <t>13.0.2</t>
         </is>
       </c>
-      <c r="B578" s="36" t="inlineStr">
+      <c r="B578" s="3" t="inlineStr">
         <is>
           <t>Embankment / non-associative+int</t>
         </is>
       </c>
-      <c r="C578" s="36" t="inlineStr">
+      <c r="C578" s="3" t="inlineStr">
         <is>
           <t>1_embankment</t>
         </is>
       </c>
-      <c r="E578" s="36" t="inlineStr">
+      <c r="E578" s="3" t="inlineStr">
         <is>
           <t>L 23, L 24</t>
         </is>
       </c>
-      <c r="F578" s="37" t="inlineStr">
+      <c r="F578" s="7" t="inlineStr">
         <is>
           <t>MohrCoulombAdvanced</t>
         </is>
       </c>
-      <c r="G578" s="36" t="n">
+      <c r="G578" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="H578" s="36" t="n">
+      <c r="H578" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="K578" s="37">
-        <f>0.38*1.06</f>
+      <c r="K578" s="3">
+        <f>38*1.06</f>
         <v/>
       </c>
-      <c r="L578" s="37" t="n">
+      <c r="L578" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="M578" s="37" t="n">
+      <c r="M578" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="P578" s="38" t="n"/>
-    </row>
-    <row r="579" customFormat="1" s="32">
-      <c r="A579" s="32" t="inlineStr">
+      <c r="P578" s="4" t="n"/>
+    </row>
+    <row r="579" customFormat="1" s="5">
+      <c r="A579" s="5" t="inlineStr">
         <is>
           <t>13.0.2</t>
         </is>
       </c>
-      <c r="B579" s="32" t="inlineStr">
+      <c r="B579" s="5" t="inlineStr">
         <is>
           <t>Sand fill / non-associative+int</t>
         </is>
       </c>
-      <c r="C579" s="32" t="inlineStr">
+      <c r="C579" s="5" t="inlineStr">
         <is>
           <t>2_sand_fill</t>
         </is>
       </c>
-      <c r="D579" s="32" t="inlineStr">
+      <c r="D579" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 23, L 22, L 19, L 20</t>
         </is>
       </c>
-      <c r="E579" s="32" t="inlineStr">
+      <c r="E579" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 20, L 25</t>
         </is>
       </c>
-      <c r="F579" s="33" t="inlineStr">
+      <c r="F579" s="30" t="inlineStr">
         <is>
           <t>MohrCoulombAdvanced</t>
         </is>
       </c>
-      <c r="G579" s="32" t="n">
+      <c r="G579" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="H579" s="32" t="n">
+      <c r="H579" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="K579" s="33">
-        <f>0.36*1.06</f>
+      <c r="K579" s="5">
+        <f>36*1.06</f>
         <v/>
       </c>
-      <c r="L579" s="33" t="n">
+      <c r="L579" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="M579" s="33" t="n">
+      <c r="M579" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="P579" s="34" t="n"/>
+      <c r="P579" s="6" t="n"/>
     </row>
     <row r="580" customFormat="1" s="8">
       <c r="A580" s="8" t="inlineStr">
@@ -33591,98 +33594,98 @@
         </is>
       </c>
     </row>
-    <row r="595" customFormat="1" s="36">
-      <c r="A595" s="36" t="inlineStr">
+    <row r="595" customFormat="1" s="3">
+      <c r="A595" s="3" t="inlineStr">
         <is>
           <t>13.13.2</t>
         </is>
       </c>
-      <c r="B595" s="36" t="inlineStr">
+      <c r="B595" s="3" t="inlineStr">
         <is>
           <t>Embankment / non-associative+int</t>
         </is>
       </c>
-      <c r="C595" s="36" t="inlineStr">
+      <c r="C595" s="3" t="inlineStr">
         <is>
           <t>1_embankment</t>
         </is>
       </c>
-      <c r="E595" s="36" t="inlineStr">
+      <c r="E595" s="3" t="inlineStr">
         <is>
           <t>L 23, L 24</t>
         </is>
       </c>
-      <c r="F595" s="37" t="inlineStr">
+      <c r="F595" s="7" t="inlineStr">
         <is>
           <t>MohrCoulombAdvanced</t>
         </is>
       </c>
-      <c r="G595" s="36" t="n">
+      <c r="G595" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="H595" s="36" t="n">
+      <c r="H595" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="K595" s="37">
-        <f>0.38*1.06</f>
+      <c r="K595" s="3">
+        <f>38*1.06</f>
         <v/>
       </c>
-      <c r="L595" s="37" t="n">
+      <c r="L595" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="M595" s="37" t="n">
+      <c r="M595" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="P595" s="38" t="n"/>
-    </row>
-    <row r="596" customFormat="1" s="32">
-      <c r="A596" s="32" t="inlineStr">
+      <c r="P595" s="4" t="n"/>
+    </row>
+    <row r="596" customFormat="1" s="5">
+      <c r="A596" s="5" t="inlineStr">
         <is>
           <t>13.13.2</t>
         </is>
       </c>
-      <c r="B596" s="32" t="inlineStr">
+      <c r="B596" s="5" t="inlineStr">
         <is>
           <t>Sand fill / non-associative+int</t>
         </is>
       </c>
-      <c r="C596" s="32" t="inlineStr">
+      <c r="C596" s="5" t="inlineStr">
         <is>
           <t>2_sand_fill</t>
         </is>
       </c>
-      <c r="D596" s="32" t="inlineStr">
+      <c r="D596" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 23, L 22, L 19, L 20</t>
         </is>
       </c>
-      <c r="E596" s="32" t="inlineStr">
+      <c r="E596" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 20, L 25</t>
         </is>
       </c>
-      <c r="F596" s="33" t="inlineStr">
+      <c r="F596" s="30" t="inlineStr">
         <is>
           <t>MohrCoulombAdvanced</t>
         </is>
       </c>
-      <c r="G596" s="32" t="n">
+      <c r="G596" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="H596" s="32" t="n">
+      <c r="H596" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="K596" s="33">
-        <f>0.36*1.06</f>
+      <c r="K596" s="5">
+        <f>36*1.06</f>
         <v/>
       </c>
-      <c r="L596" s="33" t="n">
+      <c r="L596" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="M596" s="33" t="n">
+      <c r="M596" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="P596" s="34" t="n"/>
+      <c r="P596" s="6" t="n"/>
     </row>
     <row r="597" customFormat="1" s="8">
       <c r="A597" s="8" t="inlineStr">
@@ -36118,92 +36121,92 @@
         <v>25</v>
       </c>
     </row>
-    <row r="642" customFormat="1" s="36">
-      <c r="A642" s="36" t="inlineStr">
+    <row r="642" customFormat="1" s="3">
+      <c r="A642" s="3" t="inlineStr">
         <is>
           <t>14.0.1</t>
         </is>
       </c>
-      <c r="B642" s="36" t="inlineStr">
+      <c r="B642" s="3" t="inlineStr">
         <is>
           <t>Embankment / associative+int</t>
         </is>
       </c>
-      <c r="C642" s="36" t="inlineStr">
+      <c r="C642" s="3" t="inlineStr">
         <is>
           <t>1_embankment</t>
         </is>
       </c>
-      <c r="E642" s="36" t="inlineStr">
+      <c r="E642" s="3" t="inlineStr">
         <is>
           <t>L 23, L 24</t>
         </is>
       </c>
-      <c r="F642" s="36" t="inlineStr">
+      <c r="F642" s="3" t="inlineStr">
         <is>
           <t>MohrCoulombClassic</t>
         </is>
       </c>
-      <c r="G642" s="36" t="n">
+      <c r="G642" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="H642" s="36" t="n">
+      <c r="H642" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="K642" s="37">
-        <f>0.38*1.06</f>
+      <c r="K642" s="3">
+        <f>38*1.06</f>
         <v/>
       </c>
-      <c r="L642" s="36" t="n">
+      <c r="L642" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="P642" s="38" t="n"/>
-    </row>
-    <row r="643" customFormat="1" s="32">
-      <c r="A643" s="32" t="inlineStr">
+      <c r="P642" s="4" t="n"/>
+    </row>
+    <row r="643" customFormat="1" s="5">
+      <c r="A643" s="5" t="inlineStr">
         <is>
           <t>14.0.1</t>
         </is>
       </c>
-      <c r="B643" s="32" t="inlineStr">
+      <c r="B643" s="5" t="inlineStr">
         <is>
           <t>Sand fill / associative+int</t>
         </is>
       </c>
-      <c r="C643" s="32" t="inlineStr">
+      <c r="C643" s="5" t="inlineStr">
         <is>
           <t>2_sand_fill</t>
         </is>
       </c>
-      <c r="D643" s="32" t="inlineStr">
+      <c r="D643" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 23, L 22, L 19, L 20</t>
         </is>
       </c>
-      <c r="E643" s="32" t="inlineStr">
+      <c r="E643" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 20, L 25</t>
         </is>
       </c>
-      <c r="F643" s="32" t="inlineStr">
+      <c r="F643" s="5" t="inlineStr">
         <is>
           <t>MohrCoulombClassic</t>
         </is>
       </c>
-      <c r="G643" s="32" t="n">
+      <c r="G643" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="H643" s="32" t="n">
+      <c r="H643" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="K643" s="33">
-        <f>0.36*1.06</f>
+      <c r="K643" s="5">
+        <f>36*1.06</f>
         <v/>
       </c>
-      <c r="L643" s="32" t="n">
+      <c r="L643" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="P643" s="34" t="n"/>
+      <c r="P643" s="6" t="n"/>
     </row>
     <row r="644" customFormat="1" s="8">
       <c r="A644" s="8" t="inlineStr">
@@ -37035,92 +37038,92 @@
         </is>
       </c>
     </row>
-    <row r="659" customFormat="1" s="36">
-      <c r="A659" s="36" t="inlineStr">
+    <row r="659" customFormat="1" s="3">
+      <c r="A659" s="3" t="inlineStr">
         <is>
           <t>14.14.1</t>
         </is>
       </c>
-      <c r="B659" s="36" t="inlineStr">
+      <c r="B659" s="3" t="inlineStr">
         <is>
           <t>Embankment / associative+int</t>
         </is>
       </c>
-      <c r="C659" s="36" t="inlineStr">
+      <c r="C659" s="3" t="inlineStr">
         <is>
           <t>1_embankment</t>
         </is>
       </c>
-      <c r="E659" s="36" t="inlineStr">
+      <c r="E659" s="3" t="inlineStr">
         <is>
           <t>L 23, L 24</t>
         </is>
       </c>
-      <c r="F659" s="36" t="inlineStr">
+      <c r="F659" s="3" t="inlineStr">
         <is>
           <t>MohrCoulombClassic</t>
         </is>
       </c>
-      <c r="G659" s="36" t="n">
+      <c r="G659" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="H659" s="36" t="n">
+      <c r="H659" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="K659" s="37">
-        <f>0.38*1.06</f>
+      <c r="K659" s="3">
+        <f>38*1.06</f>
         <v/>
       </c>
-      <c r="L659" s="36" t="n">
+      <c r="L659" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="P659" s="38" t="n"/>
-    </row>
-    <row r="660" customFormat="1" s="32">
-      <c r="A660" s="32" t="inlineStr">
+      <c r="P659" s="4" t="n"/>
+    </row>
+    <row r="660" customFormat="1" s="5">
+      <c r="A660" s="5" t="inlineStr">
         <is>
           <t>14.14.1</t>
         </is>
       </c>
-      <c r="B660" s="32" t="inlineStr">
+      <c r="B660" s="5" t="inlineStr">
         <is>
           <t>Sand fill / associative+int</t>
         </is>
       </c>
-      <c r="C660" s="32" t="inlineStr">
+      <c r="C660" s="5" t="inlineStr">
         <is>
           <t>2_sand_fill</t>
         </is>
       </c>
-      <c r="D660" s="32" t="inlineStr">
+      <c r="D660" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 23, L 22, L 19, L 20</t>
         </is>
       </c>
-      <c r="E660" s="32" t="inlineStr">
+      <c r="E660" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 20, L 25</t>
         </is>
       </c>
-      <c r="F660" s="32" t="inlineStr">
+      <c r="F660" s="5" t="inlineStr">
         <is>
           <t>MohrCoulombClassic</t>
         </is>
       </c>
-      <c r="G660" s="32" t="n">
+      <c r="G660" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="H660" s="32" t="n">
+      <c r="H660" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="K660" s="33">
-        <f>0.36*1.06</f>
+      <c r="K660" s="5">
+        <f>36*1.06</f>
         <v/>
       </c>
-      <c r="L660" s="32" t="n">
+      <c r="L660" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="P660" s="34" t="n"/>
+      <c r="P660" s="6" t="n"/>
     </row>
     <row r="661" customFormat="1" s="8">
       <c r="A661" s="8" t="inlineStr">
@@ -37924,98 +37927,98 @@
         <v>25</v>
       </c>
     </row>
-    <row r="676" customFormat="1" s="36">
-      <c r="A676" s="36" t="inlineStr">
+    <row r="676" customFormat="1" s="3">
+      <c r="A676" s="3" t="inlineStr">
         <is>
           <t>14.0.2</t>
         </is>
       </c>
-      <c r="B676" s="36" t="inlineStr">
+      <c r="B676" s="3" t="inlineStr">
         <is>
           <t>Embankment / non-associative+int</t>
         </is>
       </c>
-      <c r="C676" s="36" t="inlineStr">
+      <c r="C676" s="3" t="inlineStr">
         <is>
           <t>1_embankment</t>
         </is>
       </c>
-      <c r="E676" s="36" t="inlineStr">
+      <c r="E676" s="3" t="inlineStr">
         <is>
           <t>L 23, L 24</t>
         </is>
       </c>
-      <c r="F676" s="37" t="inlineStr">
+      <c r="F676" s="7" t="inlineStr">
         <is>
           <t>MohrCoulombAdvanced</t>
         </is>
       </c>
-      <c r="G676" s="36" t="n">
+      <c r="G676" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="H676" s="36" t="n">
+      <c r="H676" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="K676" s="37">
-        <f>0.38*1.06</f>
+      <c r="K676" s="3">
+        <f>38*1.06</f>
         <v/>
       </c>
-      <c r="L676" s="37" t="n">
+      <c r="L676" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="M676" s="37" t="n">
+      <c r="M676" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="P676" s="38" t="n"/>
-    </row>
-    <row r="677" customFormat="1" s="32">
-      <c r="A677" s="32" t="inlineStr">
+      <c r="P676" s="4" t="n"/>
+    </row>
+    <row r="677" customFormat="1" s="5">
+      <c r="A677" s="5" t="inlineStr">
         <is>
           <t>14.0.2</t>
         </is>
       </c>
-      <c r="B677" s="32" t="inlineStr">
+      <c r="B677" s="5" t="inlineStr">
         <is>
           <t>Sand fill / non-associative+int</t>
         </is>
       </c>
-      <c r="C677" s="32" t="inlineStr">
+      <c r="C677" s="5" t="inlineStr">
         <is>
           <t>2_sand_fill</t>
         </is>
       </c>
-      <c r="D677" s="32" t="inlineStr">
+      <c r="D677" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 23, L 22, L 19, L 20</t>
         </is>
       </c>
-      <c r="E677" s="32" t="inlineStr">
+      <c r="E677" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 20, L 25</t>
         </is>
       </c>
-      <c r="F677" s="33" t="inlineStr">
+      <c r="F677" s="30" t="inlineStr">
         <is>
           <t>MohrCoulombAdvanced</t>
         </is>
       </c>
-      <c r="G677" s="32" t="n">
+      <c r="G677" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="H677" s="32" t="n">
+      <c r="H677" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="K677" s="33">
-        <f>0.36*1.06</f>
+      <c r="K677" s="5">
+        <f>36*1.06</f>
         <v/>
       </c>
-      <c r="L677" s="33" t="n">
+      <c r="L677" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="M677" s="33" t="n">
+      <c r="M677" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="P677" s="34" t="n"/>
+      <c r="P677" s="6" t="n"/>
     </row>
     <row r="678" customFormat="1" s="8">
       <c r="A678" s="8" t="inlineStr">
@@ -38847,98 +38850,98 @@
         </is>
       </c>
     </row>
-    <row r="693" customFormat="1" s="36">
-      <c r="A693" s="36" t="inlineStr">
+    <row r="693" customFormat="1" s="3">
+      <c r="A693" s="3" t="inlineStr">
         <is>
           <t>14.14.2</t>
         </is>
       </c>
-      <c r="B693" s="36" t="inlineStr">
+      <c r="B693" s="3" t="inlineStr">
         <is>
           <t>Embankment / non-associative+int</t>
         </is>
       </c>
-      <c r="C693" s="36" t="inlineStr">
+      <c r="C693" s="3" t="inlineStr">
         <is>
           <t>1_embankment</t>
         </is>
       </c>
-      <c r="E693" s="36" t="inlineStr">
+      <c r="E693" s="3" t="inlineStr">
         <is>
           <t>L 23, L 24</t>
         </is>
       </c>
-      <c r="F693" s="37" t="inlineStr">
+      <c r="F693" s="7" t="inlineStr">
         <is>
           <t>MohrCoulombAdvanced</t>
         </is>
       </c>
-      <c r="G693" s="36" t="n">
+      <c r="G693" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="H693" s="36" t="n">
+      <c r="H693" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="K693" s="37">
-        <f>0.38*1.06</f>
+      <c r="K693" s="3">
+        <f>38*1.06</f>
         <v/>
       </c>
-      <c r="L693" s="37" t="n">
+      <c r="L693" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="M693" s="37" t="n">
+      <c r="M693" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="P693" s="38" t="n"/>
-    </row>
-    <row r="694" customFormat="1" s="32">
-      <c r="A694" s="32" t="inlineStr">
+      <c r="P693" s="4" t="n"/>
+    </row>
+    <row r="694" customFormat="1" s="5">
+      <c r="A694" s="5" t="inlineStr">
         <is>
           <t>14.14.2</t>
         </is>
       </c>
-      <c r="B694" s="32" t="inlineStr">
+      <c r="B694" s="5" t="inlineStr">
         <is>
           <t>Sand fill / non-associative+int</t>
         </is>
       </c>
-      <c r="C694" s="32" t="inlineStr">
+      <c r="C694" s="5" t="inlineStr">
         <is>
           <t>2_sand_fill</t>
         </is>
       </c>
-      <c r="D694" s="32" t="inlineStr">
+      <c r="D694" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 23, L 22, L 19, L 20</t>
         </is>
       </c>
-      <c r="E694" s="32" t="inlineStr">
+      <c r="E694" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 20, L 25</t>
         </is>
       </c>
-      <c r="F694" s="33" t="inlineStr">
+      <c r="F694" s="30" t="inlineStr">
         <is>
           <t>MohrCoulombAdvanced</t>
         </is>
       </c>
-      <c r="G694" s="32" t="n">
+      <c r="G694" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="H694" s="32" t="n">
+      <c r="H694" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="K694" s="33">
-        <f>0.36*1.06</f>
+      <c r="K694" s="5">
+        <f>36*1.06</f>
         <v/>
       </c>
-      <c r="L694" s="33" t="n">
+      <c r="L694" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="M694" s="33" t="n">
+      <c r="M694" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="P694" s="34" t="n"/>
+      <c r="P694" s="6" t="n"/>
     </row>
     <row r="695" customFormat="1" s="8">
       <c r="A695" s="8" t="inlineStr">
@@ -39742,7 +39745,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="710" s="35">
+    <row r="710">
       <c r="A710" t="inlineStr">
         <is>
           <t>15.0.0</t>
@@ -39781,7 +39784,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="711" s="35">
+    <row r="711">
       <c r="A711" t="inlineStr">
         <is>
           <t>15.0.0</t>
@@ -39825,7 +39828,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="712" s="35">
+    <row r="712">
       <c r="A712" t="inlineStr">
         <is>
           <t>15.0.0</t>
@@ -39879,7 +39882,7 @@
         </is>
       </c>
     </row>
-    <row r="713" s="35">
+    <row r="713">
       <c r="A713" t="inlineStr">
         <is>
           <t>15.0.0</t>
@@ -39933,7 +39936,7 @@
         </is>
       </c>
     </row>
-    <row r="714" s="35">
+    <row r="714">
       <c r="A714" t="inlineStr">
         <is>
           <t>15.0.0</t>
@@ -39987,7 +39990,7 @@
         </is>
       </c>
     </row>
-    <row r="715" s="35">
+    <row r="715">
       <c r="A715" t="inlineStr">
         <is>
           <t>15.0.0</t>
@@ -40041,7 +40044,7 @@
         </is>
       </c>
     </row>
-    <row r="716" s="35">
+    <row r="716">
       <c r="A716" t="inlineStr">
         <is>
           <t>15.0.0</t>
@@ -40095,7 +40098,7 @@
         </is>
       </c>
     </row>
-    <row r="717" s="35">
+    <row r="717">
       <c r="A717" t="inlineStr">
         <is>
           <t>15.0.0</t>
@@ -40149,7 +40152,7 @@
         </is>
       </c>
     </row>
-    <row r="718" s="35">
+    <row r="718">
       <c r="A718" t="inlineStr">
         <is>
           <t>15.0.0</t>
@@ -40203,7 +40206,7 @@
         </is>
       </c>
     </row>
-    <row r="719" s="35">
+    <row r="719">
       <c r="A719" t="inlineStr">
         <is>
           <t>15.0.0</t>
@@ -40257,7 +40260,7 @@
         </is>
       </c>
     </row>
-    <row r="720" s="35">
+    <row r="720">
       <c r="A720" t="inlineStr">
         <is>
           <t>15.0.0</t>
@@ -40311,7 +40314,7 @@
         </is>
       </c>
     </row>
-    <row r="721" s="35">
+    <row r="721">
       <c r="A721" t="inlineStr">
         <is>
           <t>15.0.0</t>
@@ -40365,7 +40368,7 @@
         </is>
       </c>
     </row>
-    <row r="722" s="35">
+    <row r="722">
       <c r="A722" t="inlineStr">
         <is>
           <t>15.0.0</t>
@@ -40419,7 +40422,7 @@
         </is>
       </c>
     </row>
-    <row r="723" s="35">
+    <row r="723">
       <c r="A723" t="inlineStr">
         <is>
           <t>15.0.0</t>
@@ -40473,7 +40476,7 @@
         </is>
       </c>
     </row>
-    <row r="724" s="35">
+    <row r="724">
       <c r="A724" t="inlineStr">
         <is>
           <t>15.0.0</t>
@@ -40527,7 +40530,7 @@
         </is>
       </c>
     </row>
-    <row r="725" s="35">
+    <row r="725">
       <c r="A725" t="inlineStr">
         <is>
           <t>15.0.0</t>
@@ -40581,7 +40584,7 @@
         </is>
       </c>
     </row>
-    <row r="726" s="35">
+    <row r="726">
       <c r="A726" t="inlineStr">
         <is>
           <t>15.0.0</t>
@@ -40679,92 +40682,92 @@
         <v>1</v>
       </c>
     </row>
-    <row r="728" customFormat="1" s="36">
-      <c r="A728" s="36" t="inlineStr">
+    <row r="728" customFormat="1" s="3">
+      <c r="A728" s="3" t="inlineStr">
         <is>
           <t>15.0.1</t>
         </is>
       </c>
-      <c r="B728" s="36" t="inlineStr">
+      <c r="B728" s="3" t="inlineStr">
         <is>
           <t>Embankment / associative</t>
         </is>
       </c>
-      <c r="C728" s="36" t="inlineStr">
+      <c r="C728" s="3" t="inlineStr">
         <is>
           <t>1_embankment</t>
         </is>
       </c>
-      <c r="E728" s="36" t="inlineStr">
+      <c r="E728" s="3" t="inlineStr">
         <is>
           <t>L 23, L 24</t>
         </is>
       </c>
-      <c r="F728" s="37" t="inlineStr">
+      <c r="F728" s="7" t="inlineStr">
         <is>
           <t>MohrCoulombClassic</t>
         </is>
       </c>
-      <c r="G728" s="36" t="n">
+      <c r="G728" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="H728" s="36" t="n">
+      <c r="H728" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="K728" s="37" t="n">
+      <c r="K728" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="L728" s="37" t="n">
+      <c r="L728" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="P728" s="38" t="n"/>
-    </row>
-    <row r="729" customFormat="1" s="32">
-      <c r="A729" s="32" t="inlineStr">
+      <c r="P728" s="4" t="n"/>
+    </row>
+    <row r="729" customFormat="1" s="5">
+      <c r="A729" s="5" t="inlineStr">
         <is>
           <t>15.0.1</t>
         </is>
       </c>
-      <c r="B729" s="32" t="inlineStr">
+      <c r="B729" s="5" t="inlineStr">
         <is>
           <t>Sand fill / associative</t>
         </is>
       </c>
-      <c r="C729" s="32" t="inlineStr">
+      <c r="C729" s="5" t="inlineStr">
         <is>
           <t>2_sand_fill</t>
         </is>
       </c>
-      <c r="D729" s="32" t="inlineStr">
+      <c r="D729" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 23, L 22, L 19, L 20</t>
         </is>
       </c>
-      <c r="E729" s="32" t="inlineStr">
+      <c r="E729" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 20, L 25</t>
         </is>
       </c>
-      <c r="F729" s="33" t="inlineStr">
+      <c r="F729" s="30" t="inlineStr">
         <is>
           <t>MohrCoulombClassic</t>
         </is>
       </c>
-      <c r="G729" s="32" t="n">
+      <c r="G729" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="H729" s="32" t="n">
+      <c r="H729" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="K729" s="33" t="n">
+      <c r="K729" s="30" t="n">
         <v>36</v>
       </c>
-      <c r="L729" s="33" t="n">
+      <c r="L729" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="P729" s="34" t="n"/>
-    </row>
-    <row r="730" s="35">
+      <c r="P729" s="6" t="n"/>
+    </row>
+    <row r="730">
       <c r="A730" t="inlineStr">
         <is>
           <t>15.0.1</t>
@@ -40818,7 +40821,7 @@
         </is>
       </c>
     </row>
-    <row r="731" s="35">
+    <row r="731">
       <c r="A731" t="inlineStr">
         <is>
           <t>15.0.1</t>
@@ -40872,7 +40875,7 @@
         </is>
       </c>
     </row>
-    <row r="732" s="35">
+    <row r="732">
       <c r="A732" t="inlineStr">
         <is>
           <t>15.0.1</t>
@@ -40926,7 +40929,7 @@
         </is>
       </c>
     </row>
-    <row r="733" s="35">
+    <row r="733">
       <c r="A733" t="inlineStr">
         <is>
           <t>15.0.1</t>
@@ -40980,7 +40983,7 @@
         </is>
       </c>
     </row>
-    <row r="734" s="35">
+    <row r="734">
       <c r="A734" t="inlineStr">
         <is>
           <t>15.0.1</t>
@@ -41034,7 +41037,7 @@
         </is>
       </c>
     </row>
-    <row r="735" s="35">
+    <row r="735">
       <c r="A735" t="inlineStr">
         <is>
           <t>15.0.1</t>
@@ -41088,7 +41091,7 @@
         </is>
       </c>
     </row>
-    <row r="736" s="35">
+    <row r="736">
       <c r="A736" t="inlineStr">
         <is>
           <t>15.0.1</t>
@@ -41142,7 +41145,7 @@
         </is>
       </c>
     </row>
-    <row r="737" s="35">
+    <row r="737">
       <c r="A737" t="inlineStr">
         <is>
           <t>15.0.1</t>
@@ -41196,7 +41199,7 @@
         </is>
       </c>
     </row>
-    <row r="738" s="35">
+    <row r="738">
       <c r="A738" t="inlineStr">
         <is>
           <t>15.0.1</t>
@@ -41250,7 +41253,7 @@
         </is>
       </c>
     </row>
-    <row r="739" s="35">
+    <row r="739">
       <c r="A739" t="inlineStr">
         <is>
           <t>15.0.1</t>
@@ -41304,7 +41307,7 @@
         </is>
       </c>
     </row>
-    <row r="740" s="35">
+    <row r="740">
       <c r="A740" t="inlineStr">
         <is>
           <t>15.0.1</t>
@@ -41358,7 +41361,7 @@
         </is>
       </c>
     </row>
-    <row r="741" s="35">
+    <row r="741">
       <c r="A741" t="inlineStr">
         <is>
           <t>15.0.1</t>
@@ -41412,7 +41415,7 @@
         </is>
       </c>
     </row>
-    <row r="742" s="35">
+    <row r="742">
       <c r="A742" t="inlineStr">
         <is>
           <t>15.0.1</t>
@@ -41466,7 +41469,7 @@
         </is>
       </c>
     </row>
-    <row r="743" s="35">
+    <row r="743">
       <c r="A743" t="inlineStr">
         <is>
           <t>15.0.1</t>
@@ -41520,7 +41523,7 @@
         </is>
       </c>
     </row>
-    <row r="744" s="35">
+    <row r="744">
       <c r="A744" t="inlineStr">
         <is>
           <t>15.0.1</t>
@@ -41618,98 +41621,98 @@
         <v>1</v>
       </c>
     </row>
-    <row r="746" customFormat="1" s="36">
-      <c r="A746" s="36" t="inlineStr">
+    <row r="746" customFormat="1" s="3">
+      <c r="A746" s="3" t="inlineStr">
         <is>
           <t>15.0.2</t>
         </is>
       </c>
-      <c r="B746" s="36" t="inlineStr">
+      <c r="B746" s="3" t="inlineStr">
         <is>
           <t>Embankment / non-associative</t>
         </is>
       </c>
-      <c r="C746" s="36" t="inlineStr">
+      <c r="C746" s="3" t="inlineStr">
         <is>
           <t>1_embankment</t>
         </is>
       </c>
-      <c r="E746" s="36" t="inlineStr">
+      <c r="E746" s="3" t="inlineStr">
         <is>
           <t>L 23, L 24</t>
         </is>
       </c>
-      <c r="F746" s="37" t="inlineStr">
+      <c r="F746" s="7" t="inlineStr">
         <is>
           <t>MohrCoulombAdvanced</t>
         </is>
       </c>
-      <c r="G746" s="36" t="n">
+      <c r="G746" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="H746" s="36" t="n">
+      <c r="H746" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="K746" s="37" t="n">
+      <c r="K746" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="L746" s="37" t="n">
+      <c r="L746" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="M746" s="37" t="n">
+      <c r="M746" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="P746" s="38" t="n"/>
-    </row>
-    <row r="747" customFormat="1" s="32">
-      <c r="A747" s="32" t="inlineStr">
+      <c r="P746" s="4" t="n"/>
+    </row>
+    <row r="747" customFormat="1" s="5">
+      <c r="A747" s="5" t="inlineStr">
         <is>
           <t>15.0.2</t>
         </is>
       </c>
-      <c r="B747" s="32" t="inlineStr">
+      <c r="B747" s="5" t="inlineStr">
         <is>
           <t>Sand fill / non-associative</t>
         </is>
       </c>
-      <c r="C747" s="32" t="inlineStr">
+      <c r="C747" s="5" t="inlineStr">
         <is>
           <t>2_sand_fill</t>
         </is>
       </c>
-      <c r="D747" s="32" t="inlineStr">
+      <c r="D747" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 23, L 22, L 19, L 20</t>
         </is>
       </c>
-      <c r="E747" s="32" t="inlineStr">
+      <c r="E747" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 20, L 25</t>
         </is>
       </c>
-      <c r="F747" s="33" t="inlineStr">
+      <c r="F747" s="30" t="inlineStr">
         <is>
           <t>MohrCoulombAdvanced</t>
         </is>
       </c>
-      <c r="G747" s="32" t="n">
+      <c r="G747" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="H747" s="32" t="n">
+      <c r="H747" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="K747" s="33" t="n">
+      <c r="K747" s="30" t="n">
         <v>36</v>
       </c>
-      <c r="L747" s="33" t="n">
+      <c r="L747" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="M747" s="33" t="n">
+      <c r="M747" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="P747" s="34" t="n"/>
-    </row>
-    <row r="748" s="35">
+      <c r="P747" s="6" t="n"/>
+    </row>
+    <row r="748">
       <c r="A748" t="inlineStr">
         <is>
           <t>15.0.2</t>
@@ -41763,7 +41766,7 @@
         </is>
       </c>
     </row>
-    <row r="749" s="35">
+    <row r="749">
       <c r="A749" t="inlineStr">
         <is>
           <t>15.0.2</t>
@@ -41817,7 +41820,7 @@
         </is>
       </c>
     </row>
-    <row r="750" s="35">
+    <row r="750">
       <c r="A750" t="inlineStr">
         <is>
           <t>15.0.2</t>
@@ -41871,7 +41874,7 @@
         </is>
       </c>
     </row>
-    <row r="751" s="35">
+    <row r="751">
       <c r="A751" t="inlineStr">
         <is>
           <t>15.0.2</t>
@@ -41925,7 +41928,7 @@
         </is>
       </c>
     </row>
-    <row r="752" s="35">
+    <row r="752">
       <c r="A752" t="inlineStr">
         <is>
           <t>15.0.2</t>
@@ -42563,7 +42566,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="764" s="35">
+    <row r="764">
       <c r="A764" t="inlineStr">
         <is>
           <t>16.0.0</t>
@@ -42602,7 +42605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="765" s="35">
+    <row r="765">
       <c r="A765" t="inlineStr">
         <is>
           <t>16.0.0</t>
@@ -42646,7 +42649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="766" s="35">
+    <row r="766">
       <c r="A766" t="inlineStr">
         <is>
           <t>16.0.0</t>
@@ -42700,7 +42703,7 @@
         </is>
       </c>
     </row>
-    <row r="767" s="35">
+    <row r="767">
       <c r="A767" t="inlineStr">
         <is>
           <t>16.0.0</t>
@@ -42754,7 +42757,7 @@
         </is>
       </c>
     </row>
-    <row r="768" s="35">
+    <row r="768">
       <c r="A768" t="inlineStr">
         <is>
           <t>16.0.0</t>
@@ -42808,7 +42811,7 @@
         </is>
       </c>
     </row>
-    <row r="769" s="35">
+    <row r="769">
       <c r="A769" t="inlineStr">
         <is>
           <t>16.0.0</t>
@@ -42862,7 +42865,7 @@
         </is>
       </c>
     </row>
-    <row r="770" s="35">
+    <row r="770">
       <c r="A770" t="inlineStr">
         <is>
           <t>16.0.0</t>
@@ -42916,7 +42919,7 @@
         </is>
       </c>
     </row>
-    <row r="771" s="35">
+    <row r="771">
       <c r="A771" t="inlineStr">
         <is>
           <t>16.0.0</t>
@@ -42970,7 +42973,7 @@
         </is>
       </c>
     </row>
-    <row r="772" s="35">
+    <row r="772">
       <c r="A772" t="inlineStr">
         <is>
           <t>16.0.0</t>
@@ -43024,7 +43027,7 @@
         </is>
       </c>
     </row>
-    <row r="773" s="35">
+    <row r="773">
       <c r="A773" t="inlineStr">
         <is>
           <t>16.0.0</t>
@@ -43078,7 +43081,7 @@
         </is>
       </c>
     </row>
-    <row r="774" s="35">
+    <row r="774">
       <c r="A774" t="inlineStr">
         <is>
           <t>16.0.0</t>
@@ -43132,7 +43135,7 @@
         </is>
       </c>
     </row>
-    <row r="775" s="35">
+    <row r="775">
       <c r="A775" t="inlineStr">
         <is>
           <t>16.0.0</t>
@@ -43186,7 +43189,7 @@
         </is>
       </c>
     </row>
-    <row r="776" s="35">
+    <row r="776">
       <c r="A776" t="inlineStr">
         <is>
           <t>16.0.0</t>
@@ -43240,7 +43243,7 @@
         </is>
       </c>
     </row>
-    <row r="777" s="35">
+    <row r="777">
       <c r="A777" t="inlineStr">
         <is>
           <t>16.0.0</t>
@@ -43294,7 +43297,7 @@
         </is>
       </c>
     </row>
-    <row r="778" s="35">
+    <row r="778">
       <c r="A778" t="inlineStr">
         <is>
           <t>16.0.0</t>
@@ -43348,7 +43351,7 @@
         </is>
       </c>
     </row>
-    <row r="779" s="35">
+    <row r="779">
       <c r="A779" t="inlineStr">
         <is>
           <t>16.0.0</t>
@@ -43402,7 +43405,7 @@
         </is>
       </c>
     </row>
-    <row r="780" s="35">
+    <row r="780">
       <c r="A780" t="inlineStr">
         <is>
           <t>16.0.0</t>
@@ -43500,92 +43503,92 @@
         <v>1</v>
       </c>
     </row>
-    <row r="782" customFormat="1" s="36">
-      <c r="A782" s="36" t="inlineStr">
+    <row r="782" customFormat="1" s="3">
+      <c r="A782" s="3" t="inlineStr">
         <is>
           <t>16.0.1</t>
         </is>
       </c>
-      <c r="B782" s="36" t="inlineStr">
+      <c r="B782" s="3" t="inlineStr">
         <is>
           <t>Embankment / associative</t>
         </is>
       </c>
-      <c r="C782" s="36" t="inlineStr">
+      <c r="C782" s="3" t="inlineStr">
         <is>
           <t>1_embankment</t>
         </is>
       </c>
-      <c r="E782" s="36" t="inlineStr">
+      <c r="E782" s="3" t="inlineStr">
         <is>
           <t>L 23, L 24</t>
         </is>
       </c>
-      <c r="F782" s="37" t="inlineStr">
+      <c r="F782" s="7" t="inlineStr">
         <is>
           <t>MohrCoulombClassic</t>
         </is>
       </c>
-      <c r="G782" s="36" t="n">
+      <c r="G782" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="H782" s="36" t="n">
+      <c r="H782" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="K782" s="37" t="n">
+      <c r="K782" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="L782" s="37" t="n">
+      <c r="L782" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="P782" s="38" t="n"/>
-    </row>
-    <row r="783" customFormat="1" s="32">
-      <c r="A783" s="32" t="inlineStr">
+      <c r="P782" s="4" t="n"/>
+    </row>
+    <row r="783" customFormat="1" s="5">
+      <c r="A783" s="5" t="inlineStr">
         <is>
           <t>16.0.1</t>
         </is>
       </c>
-      <c r="B783" s="32" t="inlineStr">
+      <c r="B783" s="5" t="inlineStr">
         <is>
           <t>Sand fill / associative</t>
         </is>
       </c>
-      <c r="C783" s="32" t="inlineStr">
+      <c r="C783" s="5" t="inlineStr">
         <is>
           <t>2_sand_fill</t>
         </is>
       </c>
-      <c r="D783" s="32" t="inlineStr">
+      <c r="D783" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 23, L 22, L 19, L 20</t>
         </is>
       </c>
-      <c r="E783" s="32" t="inlineStr">
+      <c r="E783" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 20, L 25</t>
         </is>
       </c>
-      <c r="F783" s="33" t="inlineStr">
+      <c r="F783" s="30" t="inlineStr">
         <is>
           <t>MohrCoulombClassic</t>
         </is>
       </c>
-      <c r="G783" s="32" t="n">
+      <c r="G783" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="H783" s="32" t="n">
+      <c r="H783" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="K783" s="33" t="n">
+      <c r="K783" s="30" t="n">
         <v>36</v>
       </c>
-      <c r="L783" s="33" t="n">
+      <c r="L783" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="P783" s="34" t="n"/>
-    </row>
-    <row r="784" s="35">
+      <c r="P783" s="6" t="n"/>
+    </row>
+    <row r="784">
       <c r="A784" t="inlineStr">
         <is>
           <t>16.0.1</t>
@@ -43639,7 +43642,7 @@
         </is>
       </c>
     </row>
-    <row r="785" s="35">
+    <row r="785">
       <c r="A785" t="inlineStr">
         <is>
           <t>16.0.1</t>
@@ -43693,7 +43696,7 @@
         </is>
       </c>
     </row>
-    <row r="786" s="35">
+    <row r="786">
       <c r="A786" t="inlineStr">
         <is>
           <t>16.0.1</t>
@@ -43747,7 +43750,7 @@
         </is>
       </c>
     </row>
-    <row r="787" s="35">
+    <row r="787">
       <c r="A787" t="inlineStr">
         <is>
           <t>16.0.1</t>
@@ -43801,7 +43804,7 @@
         </is>
       </c>
     </row>
-    <row r="788" s="35">
+    <row r="788">
       <c r="A788" t="inlineStr">
         <is>
           <t>16.0.1</t>
@@ -43855,7 +43858,7 @@
         </is>
       </c>
     </row>
-    <row r="789" s="35">
+    <row r="789">
       <c r="A789" t="inlineStr">
         <is>
           <t>16.0.1</t>
@@ -43909,7 +43912,7 @@
         </is>
       </c>
     </row>
-    <row r="790" s="35">
+    <row r="790">
       <c r="A790" t="inlineStr">
         <is>
           <t>16.0.1</t>
@@ -43963,7 +43966,7 @@
         </is>
       </c>
     </row>
-    <row r="791" s="35">
+    <row r="791">
       <c r="A791" t="inlineStr">
         <is>
           <t>16.0.1</t>
@@ -44017,7 +44020,7 @@
         </is>
       </c>
     </row>
-    <row r="792" s="35">
+    <row r="792">
       <c r="A792" t="inlineStr">
         <is>
           <t>16.0.1</t>
@@ -44071,7 +44074,7 @@
         </is>
       </c>
     </row>
-    <row r="793" s="35">
+    <row r="793">
       <c r="A793" t="inlineStr">
         <is>
           <t>16.0.1</t>
@@ -44125,7 +44128,7 @@
         </is>
       </c>
     </row>
-    <row r="794" s="35">
+    <row r="794">
       <c r="A794" t="inlineStr">
         <is>
           <t>16.0.1</t>
@@ -44179,7 +44182,7 @@
         </is>
       </c>
     </row>
-    <row r="795" s="35">
+    <row r="795">
       <c r="A795" t="inlineStr">
         <is>
           <t>16.0.1</t>
@@ -44233,7 +44236,7 @@
         </is>
       </c>
     </row>
-    <row r="796" s="35">
+    <row r="796">
       <c r="A796" t="inlineStr">
         <is>
           <t>16.0.1</t>
@@ -44287,7 +44290,7 @@
         </is>
       </c>
     </row>
-    <row r="797" s="35">
+    <row r="797">
       <c r="A797" t="inlineStr">
         <is>
           <t>16.0.1</t>
@@ -44341,7 +44344,7 @@
         </is>
       </c>
     </row>
-    <row r="798" s="35">
+    <row r="798">
       <c r="A798" t="inlineStr">
         <is>
           <t>16.0.1</t>
@@ -44439,98 +44442,98 @@
         <v>1</v>
       </c>
     </row>
-    <row r="800" customFormat="1" s="36">
-      <c r="A800" s="36" t="inlineStr">
+    <row r="800" customFormat="1" s="3">
+      <c r="A800" s="3" t="inlineStr">
         <is>
           <t>16.0.2</t>
         </is>
       </c>
-      <c r="B800" s="36" t="inlineStr">
+      <c r="B800" s="3" t="inlineStr">
         <is>
           <t>Embankment / non-associative</t>
         </is>
       </c>
-      <c r="C800" s="36" t="inlineStr">
+      <c r="C800" s="3" t="inlineStr">
         <is>
           <t>1_embankment</t>
         </is>
       </c>
-      <c r="E800" s="36" t="inlineStr">
+      <c r="E800" s="3" t="inlineStr">
         <is>
           <t>L 23, L 24</t>
         </is>
       </c>
-      <c r="F800" s="37" t="inlineStr">
+      <c r="F800" s="7" t="inlineStr">
         <is>
           <t>MohrCoulombAdvanced</t>
         </is>
       </c>
-      <c r="G800" s="36" t="n">
+      <c r="G800" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="H800" s="36" t="n">
+      <c r="H800" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="K800" s="37" t="n">
+      <c r="K800" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="L800" s="37" t="n">
+      <c r="L800" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="M800" s="37" t="n">
+      <c r="M800" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="P800" s="38" t="n"/>
-    </row>
-    <row r="801" customFormat="1" s="32">
-      <c r="A801" s="32" t="inlineStr">
+      <c r="P800" s="4" t="n"/>
+    </row>
+    <row r="801" customFormat="1" s="5">
+      <c r="A801" s="5" t="inlineStr">
         <is>
           <t>16.0.2</t>
         </is>
       </c>
-      <c r="B801" s="32" t="inlineStr">
+      <c r="B801" s="5" t="inlineStr">
         <is>
           <t>Sand fill / non-associative</t>
         </is>
       </c>
-      <c r="C801" s="32" t="inlineStr">
+      <c r="C801" s="5" t="inlineStr">
         <is>
           <t>2_sand_fill</t>
         </is>
       </c>
-      <c r="D801" s="32" t="inlineStr">
+      <c r="D801" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 23, L 22, L 19, L 20</t>
         </is>
       </c>
-      <c r="E801" s="32" t="inlineStr">
+      <c r="E801" s="5" t="inlineStr">
         <is>
           <t>L 21, L 18, L 20, L 25</t>
         </is>
       </c>
-      <c r="F801" s="33" t="inlineStr">
+      <c r="F801" s="30" t="inlineStr">
         <is>
           <t>MohrCoulombAdvanced</t>
         </is>
       </c>
-      <c r="G801" s="32" t="n">
+      <c r="G801" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="H801" s="32" t="n">
+      <c r="H801" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="K801" s="33" t="n">
+      <c r="K801" s="30" t="n">
         <v>36</v>
       </c>
-      <c r="L801" s="33" t="n">
+      <c r="L801" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="M801" s="33" t="n">
+      <c r="M801" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="P801" s="34" t="n"/>
-    </row>
-    <row r="802" s="35">
+      <c r="P801" s="6" t="n"/>
+    </row>
+    <row r="802">
       <c r="A802" t="inlineStr">
         <is>
           <t>16.0.2</t>
@@ -44584,7 +44587,7 @@
         </is>
       </c>
     </row>
-    <row r="803" s="35">
+    <row r="803">
       <c r="A803" t="inlineStr">
         <is>
           <t>16.0.2</t>
@@ -44638,7 +44641,7 @@
         </is>
       </c>
     </row>
-    <row r="804" s="35">
+    <row r="804">
       <c r="A804" t="inlineStr">
         <is>
           <t>16.0.2</t>
@@ -44692,7 +44695,7 @@
         </is>
       </c>
     </row>
-    <row r="805" s="35">
+    <row r="805">
       <c r="A805" t="inlineStr">
         <is>
           <t>16.0.2</t>
@@ -44746,7 +44749,7 @@
         </is>
       </c>
     </row>
-    <row r="806" s="35">
+    <row r="806">
       <c r="A806" t="inlineStr">
         <is>
           <t>16.0.2</t>
@@ -46536,7 +46539,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-06-30 11:37:03</t>
+          <t>2026-07-02 11:44:56</t>
         </is>
       </c>
       <c r="D44" t="b">
@@ -46562,7 +46565,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-06-30 11:37:17</t>
+          <t>2026-07-02 11:45:07</t>
         </is>
       </c>
       <c r="D45" t="b">
@@ -46588,7 +46591,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-06-30 11:37:29</t>
+          <t>2026-07-02 11:45:19</t>
         </is>
       </c>
       <c r="D46" t="b">
@@ -46614,7 +46617,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-06-30 11:37:42</t>
+          <t>2026-07-02 11:45:32</t>
         </is>
       </c>
       <c r="D47" t="b">
@@ -46640,7 +46643,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-06-30 11:37:57</t>
+          <t>2026-07-02 11:45:46</t>
         </is>
       </c>
       <c r="D48" t="b">
@@ -46666,7 +46669,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-06-30 11:38:15</t>
+          <t>2026-07-02 11:45:59</t>
         </is>
       </c>
       <c r="D49" t="b">
@@ -46692,7 +46695,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-06-30 11:38:32</t>
+          <t>2026-07-02 11:46:11</t>
         </is>
       </c>
       <c r="D50" t="b">
@@ -46718,7 +46721,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-06-30 11:38:46</t>
+          <t>2026-07-02 11:46:23</t>
         </is>
       </c>
       <c r="D51" t="b">
@@ -46744,7 +46747,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-06-30 11:39:01</t>
+          <t>2026-07-02 11:46:36</t>
         </is>
       </c>
       <c r="D52" t="b">
@@ -46770,7 +46773,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-06-30 11:39:16</t>
+          <t>2026-07-02 11:46:48</t>
         </is>
       </c>
       <c r="D53" t="b">
@@ -46796,7 +46799,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-06-30 11:39:31</t>
+          <t>2026-07-02 11:47:00</t>
         </is>
       </c>
       <c r="D54" t="b">
@@ -46822,7 +46825,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-06-30 11:39:46</t>
+          <t>2026-07-02 11:47:12</t>
         </is>
       </c>
       <c r="D55" t="b">
@@ -46848,7 +46851,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-06-30 11:40:00</t>
+          <t>2026-07-02 11:47:24</t>
         </is>
       </c>
       <c r="D56" t="b">
@@ -46874,7 +46877,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-06-30 11:40:19</t>
+          <t>2026-07-02 11:47:36</t>
         </is>
       </c>
       <c r="D57" t="b">
@@ -46900,7 +46903,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-06-30 11:40:43</t>
+          <t>2026-07-02 11:47:54</t>
         </is>
       </c>
       <c r="D58" t="b">
@@ -46926,7 +46929,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-06-30 11:41:06</t>
+          <t>2026-07-02 11:48:12</t>
         </is>
       </c>
       <c r="D59" t="b">
@@ -46952,7 +46955,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-06-30 11:41:21</t>
+          <t>2026-07-02 11:48:24</t>
         </is>
       </c>
       <c r="D60" t="b">
@@ -46978,7 +46981,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-06-30 11:41:35</t>
+          <t>2026-07-02 11:48:35</t>
         </is>
       </c>
       <c r="D61" t="b">
@@ -47004,7 +47007,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-06-30 11:41:58</t>
+          <t>2026-07-02 11:48:55</t>
         </is>
       </c>
       <c r="D62" t="b">
@@ -47030,7 +47033,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-06-30 11:42:22</t>
+          <t>2026-07-02 11:49:13</t>
         </is>
       </c>
       <c r="D63" t="b">
@@ -47056,7 +47059,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-06-30 11:42:36</t>
+          <t>2026-07-02 11:49:26</t>
         </is>
       </c>
       <c r="D64" t="b">
@@ -47082,7 +47085,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-06-30 11:42:50</t>
+          <t>2026-07-02 11:49:38</t>
         </is>
       </c>
       <c r="D65" t="b">
@@ -47108,7 +47111,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-06-30 11:43:15</t>
+          <t>2026-07-02 11:49:58</t>
         </is>
       </c>
       <c r="D66" t="b">
@@ -47134,7 +47137,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-06-30 11:43:42</t>
+          <t>2026-07-02 11:50:19</t>
         </is>
       </c>
       <c r="D67" t="b">
@@ -47160,7 +47163,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-06-30 11:43:59</t>
+          <t>2026-07-02 11:50:31</t>
         </is>
       </c>
       <c r="D68" t="b">
@@ -47186,7 +47189,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-06-30 11:44:15</t>
+          <t>2026-07-02 11:50:44</t>
         </is>
       </c>
       <c r="D69" t="b">
@@ -47212,7 +47215,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-06-30 11:44:30</t>
+          <t>2026-07-02 11:50:55</t>
         </is>
       </c>
       <c r="D70" t="b">
@@ -47238,7 +47241,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-06-30 11:44:45</t>
+          <t>2026-07-02 11:51:07</t>
         </is>
       </c>
       <c r="D71" t="b">
@@ -47264,17 +47267,17 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-06-30 11:44:59</t>
+          <t>2026-07-02 11:51:19</t>
         </is>
       </c>
       <c r="D72" t="b">
         <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>0.8222856671410353</v>
+        <v>1.063235670489106</v>
       </c>
       <c r="F72" t="n">
-        <v>0.9629181415226956</v>
+        <v>1.101671618774417</v>
       </c>
     </row>
     <row r="73">
@@ -47290,17 +47293,17 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-06-30 11:45:14</t>
+          <t>2026-07-02 11:51:33</t>
         </is>
       </c>
       <c r="D73" t="b">
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0.8222856671410353</v>
+        <v>1.063235670489106</v>
       </c>
       <c r="F73" t="n">
-        <v>0.9629181415226956</v>
+        <v>1.101671618774417</v>
       </c>
     </row>
     <row r="74">
@@ -47316,17 +47319,17 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-06-30 11:45:27</t>
+          <t>2026-07-02 11:51:46</t>
         </is>
       </c>
       <c r="D74" t="b">
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>0.8167575649161369</v>
+        <v>1.073992701934968</v>
       </c>
       <c r="F74" t="n">
-        <v>0.9537816242987386</v>
+        <v>1.117824580660754</v>
       </c>
     </row>
     <row r="75">
@@ -47342,17 +47345,17 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-06-30 11:45:40</t>
+          <t>2026-07-02 11:52:00</t>
         </is>
       </c>
       <c r="D75" t="b">
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>0.8167575649161369</v>
+        <v>1.073992701934968</v>
       </c>
       <c r="F75" t="n">
-        <v>0.9537816242987386</v>
+        <v>1.117824580660754</v>
       </c>
     </row>
     <row r="76">
@@ -47368,17 +47371,17 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-06-30 11:45:53</t>
+          <t>2026-07-02 11:52:15</t>
         </is>
       </c>
       <c r="D76" t="b">
         <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>0.8221716515904394</v>
+        <v>1.050214021054337</v>
       </c>
       <c r="F76" t="n">
-        <v>0.9628424996618994</v>
+        <v>1.090843428429197</v>
       </c>
     </row>
     <row r="77">
@@ -47394,17 +47397,17 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-06-30 11:46:07</t>
+          <t>2026-07-02 11:52:28</t>
         </is>
       </c>
       <c r="D77" t="b">
         <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>0.8221716515904394</v>
+        <v>1.050214021054337</v>
       </c>
       <c r="F77" t="n">
-        <v>0.9628424996618994</v>
+        <v>1.090843428429197</v>
       </c>
     </row>
     <row r="78">
@@ -47420,17 +47423,17 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-06-30 11:46:20</t>
+          <t>2026-07-02 11:52:40</t>
         </is>
       </c>
       <c r="D78" t="b">
         <v>1</v>
       </c>
       <c r="E78" t="n">
-        <v>0.8166435629077206</v>
+        <v>1.060442762864342</v>
       </c>
       <c r="F78" t="n">
-        <v>0.9537056075323586</v>
+        <v>1.106484240840502</v>
       </c>
     </row>
     <row r="79">
@@ -47446,17 +47449,17 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-06-30 11:46:32</t>
+          <t>2026-07-02 11:52:53</t>
         </is>
       </c>
       <c r="D79" t="b">
         <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>0.8166435629077206</v>
+        <v>1.060442762864342</v>
       </c>
       <c r="F79" t="n">
-        <v>0.9537056075323586</v>
+        <v>1.106484240840502</v>
       </c>
     </row>
     <row r="80">
@@ -47472,7 +47475,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-06-30 11:46:44</t>
+          <t>2026-07-02 11:53:07</t>
         </is>
       </c>
       <c r="D80" t="b">
@@ -47498,7 +47501,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-06-30 11:46:57</t>
+          <t>2026-07-02 11:53:20</t>
         </is>
       </c>
       <c r="D81" t="b">
@@ -47524,7 +47527,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-06-30 11:47:23</t>
+          <t>2026-07-02 11:53:46</t>
         </is>
       </c>
       <c r="D82" t="b">
@@ -47550,7 +47553,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-06-30 11:47:46</t>
+          <t>2026-07-02 11:54:06</t>
         </is>
       </c>
       <c r="D83" t="b">
@@ -47576,17 +47579,17 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-06-30 11:47:59</t>
+          <t>2026-07-02 11:54:18</t>
         </is>
       </c>
       <c r="D84" t="b">
         <v>1</v>
       </c>
       <c r="E84" t="n">
-        <v>0.7240431288525782</v>
+        <v>0.9628496121631855</v>
       </c>
       <c r="F84" t="n">
-        <v>0.8051918720311649</v>
+        <v>0.9899181302031312</v>
       </c>
     </row>
     <row r="85">
@@ -47602,17 +47605,17 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-06-30 11:48:12</t>
+          <t>2026-07-02 11:54:31</t>
         </is>
       </c>
       <c r="D85" t="b">
         <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>0.7240431288525782</v>
+        <v>0.9628496121631855</v>
       </c>
       <c r="F85" t="n">
-        <v>0.8051918720311649</v>
+        <v>0.9899181302031312</v>
       </c>
     </row>
     <row r="86">
@@ -47628,17 +47631,17 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-06-30 11:48:25</t>
+          <t>2026-07-02 11:54:43</t>
         </is>
       </c>
       <c r="D86" t="b">
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>0.7153829225121462</v>
+        <v>0.9697408537539894</v>
       </c>
       <c r="F86" t="n">
-        <v>0.812561295956683</v>
+        <v>1.001190978048176</v>
       </c>
     </row>
     <row r="87">
@@ -47654,17 +47657,17 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-06-30 11:48:38</t>
+          <t>2026-07-02 11:54:53</t>
         </is>
       </c>
       <c r="D87" t="b">
         <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>0.7153829225121462</v>
+        <v>0.9697408537539894</v>
       </c>
       <c r="F87" t="n">
-        <v>0.812561295956683</v>
+        <v>1.001190978048176</v>
       </c>
     </row>
     <row r="88">
@@ -47680,17 +47683,17 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-06-30 11:48:52</t>
+          <t>2026-07-02 11:55:05</t>
         </is>
       </c>
       <c r="D88" t="b">
         <v>1</v>
       </c>
       <c r="E88" t="n">
-        <v>0.7239293838786075</v>
+        <v>0.9511720014082856</v>
       </c>
       <c r="F88" t="n">
-        <v>0.8051208124948045</v>
+        <v>0.9744709870175174</v>
       </c>
     </row>
     <row r="89">
@@ -47706,17 +47709,17 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026-06-30 11:49:05</t>
+          <t>2026-07-02 11:55:16</t>
         </is>
       </c>
       <c r="D89" t="b">
         <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>0.7239293838786075</v>
+        <v>0.9511720014082856</v>
       </c>
       <c r="F89" t="n">
-        <v>0.8051208124948045</v>
+        <v>0.9744709870175174</v>
       </c>
     </row>
     <row r="90">
@@ -47732,17 +47735,17 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026-06-30 11:49:18</t>
+          <t>2026-07-02 11:55:34</t>
         </is>
       </c>
       <c r="D90" t="b">
         <v>1</v>
       </c>
       <c r="E90" t="n">
-        <v>0.7152692048479107</v>
+        <v>0.9579701296384895</v>
       </c>
       <c r="F90" t="n">
-        <v>0.8124902183064244</v>
+        <v>0.985684904138356</v>
       </c>
     </row>
     <row r="91">
@@ -47758,17 +47761,17 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026-06-30 11:49:32</t>
+          <t>2026-07-02 11:55:51</t>
         </is>
       </c>
       <c r="D91" t="b">
         <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>0.7152692048479107</v>
+        <v>0.9579701296384895</v>
       </c>
       <c r="F91" t="n">
-        <v>0.8124902183064244</v>
+        <v>0.985684904138356</v>
       </c>
     </row>
     <row r="92">
@@ -47784,7 +47787,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026-07-01 16:31:00</t>
+          <t>2026-07-02 11:56:07</t>
         </is>
       </c>
       <c r="D92" t="b">
@@ -47810,7 +47813,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026-07-01 16:31:17</t>
+          <t>2026-07-02 11:56:21</t>
         </is>
       </c>
       <c r="D93" t="b">
@@ -47836,7 +47839,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026-07-01 16:31:35</t>
+          <t>2026-07-02 11:56:36</t>
         </is>
       </c>
       <c r="D94" t="b">
@@ -47862,7 +47865,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026-07-01 16:31:55</t>
+          <t>2026-07-02 11:56:50</t>
         </is>
       </c>
       <c r="D95" t="b">
@@ -47888,7 +47891,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026-07-01 16:32:15</t>
+          <t>2026-07-02 11:57:06</t>
         </is>
       </c>
       <c r="D96" t="b">
@@ -47914,7 +47917,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026-07-01 16:32:32</t>
+          <t>2026-07-02 11:57:20</t>
         </is>
       </c>
       <c r="D97" t="b">
@@ -47940,7 +47943,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026-07-01 16:32:53</t>
+          <t>2026-07-02 11:57:40</t>
         </is>
       </c>
       <c r="D98" t="b">
@@ -47966,7 +47969,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026-07-01 16:33:18</t>
+          <t>2026-07-02 11:57:58</t>
         </is>
       </c>
       <c r="D99" t="b">
@@ -47992,7 +47995,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026-07-01 16:33:42</t>
+          <t>2026-07-02 11:58:17</t>
         </is>
       </c>
       <c r="D100" t="b">
@@ -48018,7 +48021,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026-07-01 16:34:06</t>
+          <t>2026-07-02 11:58:34</t>
         </is>
       </c>
       <c r="D101" t="b">
@@ -48044,7 +48047,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026-07-01 16:34:20</t>
+          <t>2026-07-02 11:58:45</t>
         </is>
       </c>
       <c r="D102" t="b">
@@ -48070,7 +48073,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026-07-01 16:34:34</t>
+          <t>2026-07-02 11:58:56</t>
         </is>
       </c>
       <c r="D103" t="b">
